--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-25.xlsx
@@ -676,7 +676,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-07-23 01:38:22</t>
+    <t>2026-07-23 03:47:31</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1273,7 @@
         <v>1.94</v>
       </c>
       <c r="G2">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H2">
         <v>5.2</v>
@@ -1282,13 +1282,13 @@
         <v>6</v>
       </c>
       <c r="J2">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K2">
         <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="M2">
         <v>1.16</v>
@@ -1321,7 +1321,7 @@
         <v>1.2</v>
       </c>
       <c r="W2">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X2">
         <v>7.2</v>
@@ -1336,7 +1336,7 @@
         <v>220</v>
       </c>
       <c r="AB2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AC2">
         <v>8</v>
@@ -1348,7 +1348,7 @@
         <v>150</v>
       </c>
       <c r="AF2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG2">
         <v>13</v>
@@ -1360,7 +1360,7 @@
         <v>200</v>
       </c>
       <c r="AJ2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK2">
         <v>46</v>
@@ -1369,7 +1369,7 @@
         <v>100</v>
       </c>
       <c r="AM2">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AN2">
         <v>40</v>
@@ -1384,10 +1384,10 @@
         <v>10</v>
       </c>
       <c r="AR2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT2">
         <v>4.9</v>
@@ -1399,7 +1399,7 @@
         <v>21</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX2">
         <v>8.800000000000001</v>
@@ -1408,88 +1408,88 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BA2">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BD2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE2">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BG2">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="s">
         <v>220</v>
@@ -1512,31 +1512,31 @@
         <v>175</v>
       </c>
       <c r="F3">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G3">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J3">
         <v>2.72</v>
       </c>
       <c r="K3">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="L3">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="M3">
         <v>1.17</v>
       </c>
       <c r="N3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O3">
         <v>1.71</v>
@@ -1545,7 +1545,7 @@
         <v>1.38</v>
       </c>
       <c r="Q3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R3">
         <v>1.13</v>
@@ -1554,16 +1554,16 @@
         <v>7</v>
       </c>
       <c r="T3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U3">
         <v>1.63</v>
       </c>
       <c r="V3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X3">
         <v>7</v>
@@ -1572,7 +1572,7 @@
         <v>8.4</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA3">
         <v>80</v>
@@ -1587,7 +1587,7 @@
         <v>19.5</v>
       </c>
       <c r="AE3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF3">
         <v>22</v>
@@ -1599,7 +1599,7 @@
         <v>34</v>
       </c>
       <c r="AI3">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ3">
         <v>75</v>
@@ -1617,7 +1617,7 @@
         <v>95</v>
       </c>
       <c r="AO3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP3">
         <v>5.9</v>
@@ -1629,7 +1629,7 @@
         <v>16.5</v>
       </c>
       <c r="AS3">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT3">
         <v>6.4</v>
@@ -1641,7 +1641,7 @@
         <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX3">
         <v>15</v>
@@ -1650,88 +1650,88 @@
         <v>12.5</v>
       </c>
       <c r="AZ3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA3">
+        <v>5.6</v>
+      </c>
+      <c r="BB3">
+        <v>5.4</v>
+      </c>
+      <c r="BC3">
+        <v>5.4</v>
+      </c>
+      <c r="BD3">
+        <v>5.6</v>
+      </c>
+      <c r="BE3">
+        <v>5.8</v>
+      </c>
+      <c r="BF3">
         <v>5.5</v>
       </c>
-      <c r="BB3">
-        <v>5.3</v>
-      </c>
-      <c r="BC3">
-        <v>5.3</v>
-      </c>
-      <c r="BD3">
+      <c r="BG3">
         <v>5.5</v>
       </c>
-      <c r="BE3">
-        <v>5.6</v>
-      </c>
-      <c r="BF3">
-        <v>5.4</v>
-      </c>
-      <c r="BG3">
-        <v>5.4</v>
-      </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="s">
         <v>220</v>
@@ -1754,13 +1754,13 @@
         <v>176</v>
       </c>
       <c r="F4">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G4">
         <v>3.6</v>
       </c>
       <c r="H4">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="I4">
         <v>2.76</v>
@@ -1769,37 +1769,37 @@
         <v>3.15</v>
       </c>
       <c r="K4">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q4">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V4">
         <v>1.57</v>
@@ -1808,103 +1808,103 @@
         <v>1.38</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
         <v>1.03</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
         <v>1.03</v>
@@ -1916,64 +1916,64 @@
         <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="BI4">
-        <v>2.46</v>
+        <v>2.86</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK4">
-        <v>1.36</v>
+        <v>5.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.36</v>
+        <v>2.56</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO4">
-        <v>1.36</v>
+        <v>4.3</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ4">
-        <v>1.36</v>
+        <v>2.38</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS4">
-        <v>1.36</v>
+        <v>2.46</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU4">
-        <v>1.36</v>
+        <v>3.8</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW4">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY4">
-        <v>1.36</v>
+        <v>2.42</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA4">
-        <v>1.36</v>
+        <v>2.42</v>
       </c>
       <c r="CB4" t="s">
         <v>220</v>
@@ -1999,7 +1999,7 @@
         <v>1.49</v>
       </c>
       <c r="G5">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H5">
         <v>6.4</v>
@@ -2011,7 +2011,7 @@
         <v>4.7</v>
       </c>
       <c r="K5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2023,22 +2023,22 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="R5">
         <v>1.56</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="T5">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="U5">
         <v>2.08</v>
@@ -2047,7 +2047,7 @@
         <v>1.15</v>
       </c>
       <c r="W5">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="X5">
         <v>29</v>
@@ -2062,7 +2062,7 @@
         <v>230</v>
       </c>
       <c r="AB5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
         <v>13.5</v>
@@ -2113,7 +2113,7 @@
         <v>38</v>
       </c>
       <c r="AS5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT5">
         <v>7.8</v>
@@ -2125,7 +2125,7 @@
         <v>19</v>
       </c>
       <c r="AW5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX5">
         <v>7.8</v>
@@ -2137,7 +2137,7 @@
         <v>18</v>
       </c>
       <c r="BA5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB5">
         <v>13</v>
@@ -2149,13 +2149,13 @@
         <v>21</v>
       </c>
       <c r="BE5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF5">
         <v>5.3</v>
       </c>
       <c r="BG5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2238,10 +2238,10 @@
         <v>178</v>
       </c>
       <c r="F6">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G6">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="H6">
         <v>7.6</v>
@@ -2250,10 +2250,10 @@
         <v>9.4</v>
       </c>
       <c r="J6">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2262,25 +2262,25 @@
         <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O6">
         <v>1.4</v>
       </c>
       <c r="P6">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
         <v>4.1</v>
       </c>
       <c r="T6">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="U6">
         <v>1.68</v>
@@ -2289,7 +2289,7 @@
         <v>1.12</v>
       </c>
       <c r="W6">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="X6">
         <v>13.5</v>
@@ -2298,16 +2298,16 @@
         <v>24</v>
       </c>
       <c r="Z6">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA6">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AB6">
         <v>7.2</v>
       </c>
       <c r="AC6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6">
         <v>38</v>
@@ -2316,7 +2316,7 @@
         <v>200</v>
       </c>
       <c r="AF6">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AG6">
         <v>12</v>
@@ -2325,7 +2325,7 @@
         <v>34</v>
       </c>
       <c r="AI6">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AJ6">
         <v>16.5</v>
@@ -2337,13 +2337,13 @@
         <v>55</v>
       </c>
       <c r="AM6">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AN6">
         <v>13.5</v>
       </c>
       <c r="AO6">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="AP6">
         <v>10</v>
@@ -2352,22 +2352,22 @@
         <v>17.5</v>
       </c>
       <c r="AR6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AS6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT6">
         <v>5.6</v>
       </c>
       <c r="AU6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV6">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AW6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX6">
         <v>7</v>
@@ -2376,10 +2376,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BA6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB6">
         <v>12</v>
@@ -2388,16 +2388,16 @@
         <v>16.5</v>
       </c>
       <c r="BD6">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BE6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF6">
         <v>9</v>
       </c>
       <c r="BG6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2483,16 +2483,16 @@
         <v>1.44</v>
       </c>
       <c r="G7">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="I7">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="K7">
         <v>5.1</v>
@@ -2504,22 +2504,22 @@
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O7">
         <v>1.25</v>
       </c>
       <c r="P7">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q7">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="R7">
         <v>1.42</v>
       </c>
       <c r="S7">
-        <v>2.94</v>
+        <v>2.72</v>
       </c>
       <c r="T7">
         <v>1.92</v>
@@ -2528,10 +2528,10 @@
         <v>1.89</v>
       </c>
       <c r="V7">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W7">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="X7">
         <v>22</v>
@@ -2543,7 +2543,7 @@
         <v>85</v>
       </c>
       <c r="AA7">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AB7">
         <v>9</v>
@@ -2552,19 +2552,19 @@
         <v>11.5</v>
       </c>
       <c r="AD7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AE7">
         <v>150</v>
       </c>
       <c r="AF7">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AI7">
         <v>130</v>
@@ -2576,7 +2576,7 @@
         <v>16.5</v>
       </c>
       <c r="AL7">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM7">
         <v>160</v>
@@ -2588,58 +2588,58 @@
         <v>190</v>
       </c>
       <c r="AP7">
-        <v>14</v>
+        <v>5.4</v>
       </c>
       <c r="AQ7">
-        <v>20</v>
+        <v>5.7</v>
       </c>
       <c r="AR7">
+        <v>6.6</v>
+      </c>
+      <c r="AS7">
         <v>7</v>
       </c>
-      <c r="AS7">
-        <v>7.4</v>
-      </c>
       <c r="AT7">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="AU7">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AV7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AW7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX7">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AY7">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>5.7</v>
       </c>
       <c r="BA7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB7">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="BC7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="BD7">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BE7">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF7">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="BG7">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2722,22 +2722,22 @@
         <v>180</v>
       </c>
       <c r="F8">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H8">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I8">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="J8">
         <v>3.2</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2746,22 +2746,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="O8">
         <v>1.29</v>
       </c>
       <c r="P8">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="Q8">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="R8">
         <v>1.18</v>
       </c>
       <c r="S8">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2770,10 +2770,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W8">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2964,7 +2964,7 @@
         <v>181</v>
       </c>
       <c r="F9">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G9">
         <v>6.2</v>
@@ -2976,13 +2976,13 @@
         <v>1.76</v>
       </c>
       <c r="J9">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M9">
         <v>1.06</v>
@@ -3024,7 +3024,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z9">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA9">
         <v>18.5</v>
@@ -3069,7 +3069,7 @@
         <v>95</v>
       </c>
       <c r="AO9">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AP9">
         <v>14.5</v>
@@ -3084,7 +3084,7 @@
         <v>15.5</v>
       </c>
       <c r="AT9">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU9">
         <v>8.199999999999999</v>
@@ -3093,97 +3093,97 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW9">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX9">
         <v>27</v>
       </c>
       <c r="AY9">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AZ9">
         <v>17</v>
       </c>
       <c r="BA9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB9">
+        <v>7.2</v>
+      </c>
+      <c r="BC9">
+        <v>6.8</v>
+      </c>
+      <c r="BD9">
+        <v>6.8</v>
+      </c>
+      <c r="BE9">
+        <v>7.2</v>
+      </c>
+      <c r="BF9">
         <v>7</v>
-      </c>
-      <c r="BC9">
-        <v>6.6</v>
-      </c>
-      <c r="BD9">
-        <v>6.6</v>
-      </c>
-      <c r="BE9">
-        <v>6.8</v>
-      </c>
-      <c r="BF9">
-        <v>6.8</v>
       </c>
       <c r="BG9">
         <v>8</v>
       </c>
       <c r="BH9">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="BI9">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK9">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.3</v>
+        <v>14</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO9">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.3</v>
+        <v>11.5</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.3</v>
+        <v>12</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BU9">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW9">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.3</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="s">
         <v>220</v>
@@ -3206,22 +3206,22 @@
         <v>182</v>
       </c>
       <c r="F10">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="G10">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I10">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J10">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3233,43 +3233,43 @@
         <v>4.8</v>
       </c>
       <c r="O10">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q10">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R10">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S10">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="T10">
         <v>1.62</v>
       </c>
       <c r="U10">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W10">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="X10">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y10">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="Z10">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AA10">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AB10">
         <v>12.5</v>
@@ -3293,7 +3293,7 @@
         <v>16</v>
       </c>
       <c r="AI10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ10">
         <v>32</v>
@@ -3305,7 +3305,7 @@
         <v>30</v>
       </c>
       <c r="AM10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN10">
         <v>11.5</v>
@@ -3320,10 +3320,10 @@
         <v>15.5</v>
       </c>
       <c r="AR10">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AT10">
         <v>11</v>
@@ -3350,16 +3350,16 @@
         <v>34</v>
       </c>
       <c r="BB10">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC10">
         <v>17.5</v>
       </c>
       <c r="BD10">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE10">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BF10">
         <v>8.4</v>
@@ -3448,23 +3448,23 @@
         <v>183</v>
       </c>
       <c r="F11">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G11">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="H11">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="I11">
+        <v>4.2</v>
+      </c>
+      <c r="J11">
+        <v>4</v>
+      </c>
+      <c r="K11">
         <v>4.8</v>
       </c>
-      <c r="J11">
-        <v>3.75</v>
-      </c>
-      <c r="K11">
-        <v>7</v>
-      </c>
       <c r="L11">
         <v>0</v>
       </c>
@@ -3478,10 +3478,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.07</v>
+        <v>2.62</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3690,40 +3690,40 @@
         <v>184</v>
       </c>
       <c r="F12">
+        <v>2.32</v>
+      </c>
+      <c r="G12">
+        <v>2.54</v>
+      </c>
+      <c r="H12">
+        <v>3.2</v>
+      </c>
+      <c r="I12">
+        <v>3.6</v>
+      </c>
+      <c r="J12">
+        <v>3.2</v>
+      </c>
+      <c r="K12">
+        <v>3.55</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.76</v>
+      </c>
+      <c r="Q12">
         <v>2.12</v>
-      </c>
-      <c r="G12">
-        <v>2.84</v>
-      </c>
-      <c r="H12">
-        <v>2.82</v>
-      </c>
-      <c r="I12">
-        <v>4.2</v>
-      </c>
-      <c r="J12">
-        <v>3.15</v>
-      </c>
-      <c r="K12">
-        <v>5.8</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>1.61</v>
-      </c>
-      <c r="Q12">
-        <v>1.01</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3932,22 +3932,22 @@
         <v>185</v>
       </c>
       <c r="F13">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="G13">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="H13">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="I13">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J13">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K13">
-        <v>5.9</v>
+        <v>3.75</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3962,10 +3962,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4177,7 +4177,7 @@
         <v>3.5</v>
       </c>
       <c r="G14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H14">
         <v>2.12</v>
@@ -4186,7 +4186,7 @@
         <v>2.32</v>
       </c>
       <c r="J14">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K14">
         <v>4</v>
@@ -4204,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q14">
         <v>1.86</v>
@@ -4425,13 +4425,13 @@
         <v>3.95</v>
       </c>
       <c r="I15">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J15">
         <v>3.8</v>
       </c>
       <c r="K15">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4446,7 +4446,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q15">
         <v>1.67</v>
@@ -4906,16 +4906,16 @@
         <v>2.3</v>
       </c>
       <c r="H17">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I17">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J17">
         <v>3.9</v>
       </c>
       <c r="K17">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4930,7 +4930,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q17">
         <v>1.63</v>
@@ -5142,19 +5142,19 @@
         <v>190</v>
       </c>
       <c r="F18">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G18">
         <v>5.3</v>
       </c>
       <c r="H18">
+        <v>1.74</v>
+      </c>
+      <c r="I18">
         <v>1.76</v>
       </c>
-      <c r="I18">
-        <v>1.77</v>
-      </c>
       <c r="J18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K18">
         <v>4.3</v>
@@ -5172,10 +5172,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q18">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5629,19 +5629,19 @@
         <v>4.1</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="I20">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="J20">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K20">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5659,7 +5659,7 @@
         <v>1.96</v>
       </c>
       <c r="Q20">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5871,19 +5871,19 @@
         <v>2.88</v>
       </c>
       <c r="G21">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H21">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I21">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J21">
         <v>3.6</v>
       </c>
       <c r="K21">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5898,10 +5898,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q21">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6358,7 +6358,7 @@
         <v>38</v>
       </c>
       <c r="H23">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I23">
         <v>36</v>
@@ -6836,23 +6836,23 @@
         <v>197</v>
       </c>
       <c r="F25">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="G25">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="H25">
+        <v>5.5</v>
+      </c>
+      <c r="I25">
+        <v>7.6</v>
+      </c>
+      <c r="J25">
+        <v>4.3</v>
+      </c>
+      <c r="K25">
         <v>4.9</v>
       </c>
-      <c r="I25">
-        <v>13.5</v>
-      </c>
-      <c r="J25">
-        <v>3.95</v>
-      </c>
-      <c r="K25">
-        <v>8.199999999999999</v>
-      </c>
       <c r="L25">
         <v>0</v>
       </c>
@@ -6866,10 +6866,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="Q25">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7320,220 +7320,220 @@
         <v>199</v>
       </c>
       <c r="F27">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G27">
+        <v>3.8</v>
+      </c>
+      <c r="H27">
+        <v>2.4</v>
+      </c>
+      <c r="I27">
+        <v>2.64</v>
+      </c>
+      <c r="J27">
+        <v>3</v>
+      </c>
+      <c r="K27">
+        <v>3.25</v>
+      </c>
+      <c r="L27">
+        <v>1.45</v>
+      </c>
+      <c r="M27">
+        <v>1.09</v>
+      </c>
+      <c r="N27">
+        <v>2.74</v>
+      </c>
+      <c r="O27">
+        <v>1.49</v>
+      </c>
+      <c r="P27">
+        <v>1.58</v>
+      </c>
+      <c r="Q27">
+        <v>2.46</v>
+      </c>
+      <c r="R27">
+        <v>1.21</v>
+      </c>
+      <c r="S27">
+        <v>4.6</v>
+      </c>
+      <c r="T27">
+        <v>2</v>
+      </c>
+      <c r="U27">
+        <v>1.85</v>
+      </c>
+      <c r="V27">
+        <v>1.6</v>
+      </c>
+      <c r="W27">
+        <v>1.37</v>
+      </c>
+      <c r="X27">
+        <v>11.5</v>
+      </c>
+      <c r="Y27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z27">
+        <v>18</v>
+      </c>
+      <c r="AA27">
+        <v>48</v>
+      </c>
+      <c r="AB27">
+        <v>12.5</v>
+      </c>
+      <c r="AC27">
+        <v>8.6</v>
+      </c>
+      <c r="AD27">
+        <v>15</v>
+      </c>
+      <c r="AE27">
+        <v>42</v>
+      </c>
+      <c r="AF27">
+        <v>28</v>
+      </c>
+      <c r="AG27">
+        <v>19</v>
+      </c>
+      <c r="AH27">
+        <v>26</v>
+      </c>
+      <c r="AI27">
+        <v>70</v>
+      </c>
+      <c r="AJ27">
+        <v>90</v>
+      </c>
+      <c r="AK27">
+        <v>65</v>
+      </c>
+      <c r="AL27">
+        <v>90</v>
+      </c>
+      <c r="AM27">
+        <v>190</v>
+      </c>
+      <c r="AN27">
+        <v>85</v>
+      </c>
+      <c r="AO27">
+        <v>44</v>
+      </c>
+      <c r="AP27">
+        <v>7</v>
+      </c>
+      <c r="AQ27">
+        <v>6</v>
+      </c>
+      <c r="AR27">
+        <v>11</v>
+      </c>
+      <c r="AS27">
         <v>3.95</v>
       </c>
-      <c r="H27">
-        <v>2.38</v>
-      </c>
-      <c r="I27">
-        <v>2.68</v>
-      </c>
-      <c r="J27">
-        <v>3.05</v>
-      </c>
-      <c r="K27">
-        <v>3.35</v>
-      </c>
-      <c r="L27">
-        <v>1.01</v>
-      </c>
-      <c r="M27">
-        <v>1.01</v>
-      </c>
-      <c r="N27">
-        <v>2.62</v>
-      </c>
-      <c r="O27">
-        <v>1.46</v>
-      </c>
-      <c r="P27">
-        <v>1.54</v>
-      </c>
-      <c r="Q27">
-        <v>2.4</v>
-      </c>
-      <c r="R27">
-        <v>1.18</v>
-      </c>
-      <c r="S27">
-        <v>4.5</v>
-      </c>
-      <c r="T27">
-        <v>1.11</v>
-      </c>
-      <c r="U27">
-        <v>1.84</v>
-      </c>
-      <c r="V27">
-        <v>1.59</v>
-      </c>
-      <c r="W27">
-        <v>1.34</v>
-      </c>
-      <c r="X27">
-        <v>1000</v>
-      </c>
-      <c r="Y27">
-        <v>1000</v>
-      </c>
-      <c r="Z27">
-        <v>1000</v>
-      </c>
-      <c r="AA27">
-        <v>1000</v>
-      </c>
-      <c r="AB27">
-        <v>1000</v>
-      </c>
-      <c r="AC27">
-        <v>1000</v>
-      </c>
-      <c r="AD27">
-        <v>1000</v>
-      </c>
-      <c r="AE27">
-        <v>1000</v>
-      </c>
-      <c r="AF27">
-        <v>1000</v>
-      </c>
-      <c r="AG27">
-        <v>1000</v>
-      </c>
-      <c r="AH27">
-        <v>1000</v>
-      </c>
-      <c r="AI27">
-        <v>1000</v>
-      </c>
-      <c r="AJ27">
-        <v>1000</v>
-      </c>
-      <c r="AK27">
-        <v>1000</v>
-      </c>
-      <c r="AL27">
-        <v>1000</v>
-      </c>
-      <c r="AM27">
-        <v>1000</v>
-      </c>
-      <c r="AN27">
-        <v>1000</v>
-      </c>
-      <c r="AO27">
-        <v>1000</v>
-      </c>
-      <c r="AP27">
-        <v>1.01</v>
-      </c>
-      <c r="AQ27">
-        <v>1.01</v>
-      </c>
-      <c r="AR27">
-        <v>1.01</v>
-      </c>
-      <c r="AS27">
-        <v>1.01</v>
-      </c>
       <c r="AT27">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU27">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV27">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW27">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX27">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY27">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ27">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA27">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB27">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF27">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG27">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH27">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI27">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK27">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL27">
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO27">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ27">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS27">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU27">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW27">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX27">
         <v>1000</v>
       </c>
       <c r="BY27">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ27">
         <v>0</v>
@@ -7562,22 +7562,22 @@
         <v>200</v>
       </c>
       <c r="F28">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="G28">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H28">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="I28">
-        <v>870</v>
+        <v>6.4</v>
       </c>
       <c r="J28">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="K28">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -7592,10 +7592,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q28">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -7810,7 +7810,7 @@
         <v>2.54</v>
       </c>
       <c r="H29">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I29">
         <v>3.15</v>
@@ -7834,7 +7834,7 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q29">
         <v>1.81</v>
@@ -8046,16 +8046,16 @@
         <v>202</v>
       </c>
       <c r="F30">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G30">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H30">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I30">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J30">
         <v>4.3</v>
@@ -8088,10 +8088,10 @@
         <v>0</v>
       </c>
       <c r="T30">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U30">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -8103,13 +8103,13 @@
         <v>16</v>
       </c>
       <c r="Y30">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z30">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA30">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="AB30">
         <v>8</v>
@@ -8121,16 +8121,16 @@
         <v>34</v>
       </c>
       <c r="AE30">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF30">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AG30">
         <v>11</v>
       </c>
       <c r="AH30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI30">
         <v>140</v>
@@ -8145,40 +8145,40 @@
         <v>48</v>
       </c>
       <c r="AM30">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN30">
         <v>8.800000000000001</v>
       </c>
       <c r="AO30">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="AP30">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ30">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="AR30">
         <v>7.4</v>
       </c>
       <c r="AS30">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT30">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AU30">
         <v>8.800000000000001</v>
       </c>
       <c r="AV30">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW30">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX30">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="AY30">
         <v>8.6</v>
@@ -8187,22 +8187,22 @@
         <v>6.4</v>
       </c>
       <c r="BA30">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB30">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="BC30">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD30">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE30">
         <v>7.8</v>
       </c>
       <c r="BF30">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BG30">
         <v>7.8</v>
@@ -8288,13 +8288,13 @@
         <v>203</v>
       </c>
       <c r="F31">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G31">
         <v>2.48</v>
       </c>
       <c r="H31">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I31">
         <v>3.15</v>
@@ -8318,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q31">
         <v>1.74</v>
@@ -8536,49 +8536,49 @@
         <v>2.04</v>
       </c>
       <c r="H32">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I32">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J32">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="K32">
         <v>4.5</v>
       </c>
       <c r="L32">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M32">
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O32">
         <v>1.18</v>
       </c>
       <c r="P32">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q32">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R32">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S32">
         <v>2.34</v>
       </c>
       <c r="T32">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U32">
         <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W32">
         <v>1.96</v>
@@ -8593,22 +8593,22 @@
         <v>34</v>
       </c>
       <c r="AA32">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB32">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC32">
         <v>12.5</v>
       </c>
       <c r="AD32">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE32">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF32">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG32">
         <v>13.5</v>
@@ -8617,139 +8617,139 @@
         <v>16.5</v>
       </c>
       <c r="AI32">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ32">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK32">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL32">
         <v>28</v>
       </c>
       <c r="AM32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN32">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO32">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP32">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ32">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AR32">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS32">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT32">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU32">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AV32">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AW32">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX32">
+        <v>11</v>
+      </c>
+      <c r="AY32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ32">
         <v>11.5</v>
       </c>
-      <c r="AY32">
-        <v>9.4</v>
-      </c>
-      <c r="AZ32">
+      <c r="BA32">
+        <v>5</v>
+      </c>
+      <c r="BB32">
+        <v>16.5</v>
+      </c>
+      <c r="BC32">
         <v>13</v>
-      </c>
-      <c r="BA32">
-        <v>4.9</v>
-      </c>
-      <c r="BB32">
-        <v>20</v>
-      </c>
-      <c r="BC32">
-        <v>13.5</v>
       </c>
       <c r="BD32">
         <v>19</v>
       </c>
       <c r="BE32">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF32">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG32">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI32">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BJ32">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK32">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL32">
         <v>1000</v>
       </c>
       <c r="BM32">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN32">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO32">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP32">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ32">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR32">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS32">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT32">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU32">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV32">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BW32">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX32">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY32">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ32">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA32">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB32" t="s">
         <v>220</v>
@@ -8772,22 +8772,22 @@
         <v>205</v>
       </c>
       <c r="F33">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G33">
-        <v>2.96</v>
+        <v>2.66</v>
       </c>
       <c r="H33">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="I33">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="J33">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K33">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -8805,7 +8805,7 @@
         <v>1.9</v>
       </c>
       <c r="Q33">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -9056,7 +9056,7 @@
         <v>0</v>
       </c>
       <c r="T34">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U34">
         <v>2</v>
@@ -9089,7 +9089,7 @@
         <v>13.5</v>
       </c>
       <c r="AE34">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF34">
         <v>19.5</v>
@@ -9170,7 +9170,7 @@
         <v>7.8</v>
       </c>
       <c r="BF34">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG34">
         <v>6.6</v>
@@ -9256,10 +9256,10 @@
         <v>207</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G35">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H35">
         <v>2.32</v>
@@ -9268,10 +9268,10 @@
         <v>2.4</v>
       </c>
       <c r="J35">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K35">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9498,16 +9498,16 @@
         <v>208</v>
       </c>
       <c r="F36">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G36">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H36">
         <v>5.3</v>
       </c>
       <c r="I36">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J36">
         <v>3.3</v>
@@ -9516,10 +9516,10 @@
         <v>3.6</v>
       </c>
       <c r="L36">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M36">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N36">
         <v>2.66</v>
@@ -9531,7 +9531,7 @@
         <v>1.55</v>
       </c>
       <c r="Q36">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R36">
         <v>1.2</v>
@@ -9588,7 +9588,7 @@
         <v>150</v>
       </c>
       <c r="AJ36">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK36">
         <v>30</v>
@@ -9603,16 +9603,16 @@
         <v>25</v>
       </c>
       <c r="AO36">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP36">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ36">
         <v>10.5</v>
       </c>
       <c r="AR36">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="AS36">
         <v>5</v>
@@ -9624,16 +9624,16 @@
         <v>6.2</v>
       </c>
       <c r="AV36">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW36">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX36">
         <v>8.6</v>
       </c>
       <c r="AY36">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ36">
         <v>20</v>
@@ -9642,82 +9642,82 @@
         <v>5</v>
       </c>
       <c r="BB36">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BC36">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BD36">
         <v>4.8</v>
       </c>
       <c r="BE36">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF36">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG36">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH36">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI36">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BJ36">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK36">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN36">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO36">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP36">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ36">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR36">
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT36">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU36">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV36">
         <v>1000</v>
       </c>
       <c r="BW36">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BX36">
         <v>1000</v>
       </c>
       <c r="BY36">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BZ36">
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB36" t="s">
         <v>220</v>
@@ -9988,16 +9988,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H38">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I38">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="J38">
         <v>4.3</v>
       </c>
       <c r="K38">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -10012,10 +10012,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q38">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10039,7 +10039,7 @@
         <v>21</v>
       </c>
       <c r="Y38">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z38">
         <v>11</v>
@@ -10048,7 +10048,7 @@
         <v>16.5</v>
       </c>
       <c r="AB38">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC38">
         <v>12</v>
@@ -10060,40 +10060,40 @@
         <v>19</v>
       </c>
       <c r="AF38">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG38">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH38">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI38">
         <v>36</v>
       </c>
       <c r="AJ38">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AK38">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL38">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM38">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN38">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO38">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP38">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ38">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR38">
         <v>7.4</v>
@@ -10102,10 +10102,10 @@
         <v>11</v>
       </c>
       <c r="AT38">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AU38">
-        <v>9</v>
+        <v>3.85</v>
       </c>
       <c r="AV38">
         <v>8.800000000000001</v>
@@ -10114,7 +10114,7 @@
         <v>12.5</v>
       </c>
       <c r="AX38">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY38">
         <v>20</v>
@@ -10123,25 +10123,25 @@
         <v>17</v>
       </c>
       <c r="BA38">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB38">
+        <v>5.5</v>
+      </c>
+      <c r="BC38">
         <v>5.4</v>
       </c>
-      <c r="BC38">
-        <v>5.2</v>
-      </c>
       <c r="BD38">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE38">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF38">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG38">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="BH38">
         <v>0</v>
@@ -10224,7 +10224,7 @@
         <v>211</v>
       </c>
       <c r="F39">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G39">
         <v>1.6</v>
@@ -10233,7 +10233,7 @@
         <v>6.6</v>
       </c>
       <c r="I39">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J39">
         <v>4.4</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q39">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10708,23 +10708,23 @@
         <v>213</v>
       </c>
       <c r="F41">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G41">
+        <v>3.2</v>
+      </c>
+      <c r="H41">
+        <v>2.44</v>
+      </c>
+      <c r="I41">
+        <v>2.66</v>
+      </c>
+      <c r="J41">
+        <v>3.4</v>
+      </c>
+      <c r="K41">
         <v>3.8</v>
       </c>
-      <c r="H41">
-        <v>2.3</v>
-      </c>
-      <c r="I41">
-        <v>3</v>
-      </c>
-      <c r="J41">
-        <v>3.05</v>
-      </c>
-      <c r="K41">
-        <v>4.7</v>
-      </c>
       <c r="L41">
         <v>0</v>
       </c>
@@ -10738,10 +10738,10 @@
         <v>0</v>
       </c>
       <c r="P41">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="Q41">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="R41">
         <v>0</v>
@@ -11192,22 +11192,22 @@
         <v>215</v>
       </c>
       <c r="F43">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="G43">
         <v>1.44</v>
       </c>
       <c r="H43">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="I43">
-        <v>870</v>
+        <v>11</v>
       </c>
       <c r="J43">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="K43">
-        <v>9.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11225,7 +11225,7 @@
         <v>2.2</v>
       </c>
       <c r="Q43">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -11676,16 +11676,16 @@
         <v>217</v>
       </c>
       <c r="F45">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="G45">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H45">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="I45">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J45">
         <v>2.84</v>
@@ -11706,7 +11706,7 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q45">
         <v>2.84</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-25.xlsx
@@ -676,7 +676,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-07-23 03:47:31</t>
+    <t>2026-07-23 05:56:42</t>
   </si>
 </sst>
 </file>
@@ -1273,10 +1273,10 @@
         <v>1.94</v>
       </c>
       <c r="G2">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I2">
         <v>6</v>
@@ -1321,7 +1321,7 @@
         <v>1.2</v>
       </c>
       <c r="W2">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="X2">
         <v>7.2</v>
@@ -1384,7 +1384,7 @@
         <v>10</v>
       </c>
       <c r="AR2">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="AS2">
         <v>9.6</v>
@@ -1515,7 +1515,7 @@
         <v>2.9</v>
       </c>
       <c r="G3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -1524,7 +1524,7 @@
         <v>3.35</v>
       </c>
       <c r="J3">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K3">
         <v>2.96</v>
@@ -1545,7 +1545,7 @@
         <v>1.38</v>
       </c>
       <c r="Q3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R3">
         <v>1.13</v>
@@ -1569,7 +1569,7 @@
         <v>7</v>
       </c>
       <c r="Y3">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="Z3">
         <v>23</v>
@@ -1581,7 +1581,7 @@
         <v>9</v>
       </c>
       <c r="AC3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
         <v>19.5</v>
@@ -1593,7 +1593,7 @@
         <v>22</v>
       </c>
       <c r="AG3">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH3">
         <v>34</v>
@@ -1629,7 +1629,7 @@
         <v>16.5</v>
       </c>
       <c r="AS3">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT3">
         <v>6.4</v>
@@ -1641,7 +1641,7 @@
         <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AX3">
         <v>15</v>
@@ -1650,28 +1650,28 @@
         <v>12.5</v>
       </c>
       <c r="AZ3">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BA3">
+        <v>5.4</v>
+      </c>
+      <c r="BB3">
+        <v>5.3</v>
+      </c>
+      <c r="BC3">
+        <v>5.2</v>
+      </c>
+      <c r="BD3">
+        <v>5.4</v>
+      </c>
+      <c r="BE3">
         <v>5.6</v>
       </c>
-      <c r="BB3">
+      <c r="BF3">
         <v>5.4</v>
       </c>
-      <c r="BC3">
+      <c r="BG3">
         <v>5.4</v>
-      </c>
-      <c r="BD3">
-        <v>5.6</v>
-      </c>
-      <c r="BE3">
-        <v>5.8</v>
-      </c>
-      <c r="BF3">
-        <v>5.5</v>
-      </c>
-      <c r="BG3">
-        <v>5.5</v>
       </c>
       <c r="BH3">
         <v>2.48</v>
@@ -1754,64 +1754,64 @@
         <v>176</v>
       </c>
       <c r="F4">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H4">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I4">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="J4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
+        <v>3.4</v>
+      </c>
+      <c r="O4">
+        <v>1.35</v>
+      </c>
+      <c r="P4">
+        <v>1.77</v>
+      </c>
+      <c r="Q4">
+        <v>2.02</v>
+      </c>
+      <c r="R4">
+        <v>1.31</v>
+      </c>
+      <c r="S4">
         <v>3.2</v>
       </c>
-      <c r="O4">
-        <v>1.37</v>
-      </c>
-      <c r="P4">
-        <v>1.76</v>
-      </c>
-      <c r="Q4">
-        <v>2.08</v>
-      </c>
-      <c r="R4">
-        <v>1.29</v>
-      </c>
-      <c r="S4">
-        <v>3.4</v>
-      </c>
       <c r="T4">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U4">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W4">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z4">
         <v>19.5</v>
@@ -1820,7 +1820,7 @@
         <v>44</v>
       </c>
       <c r="AB4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC4">
         <v>9.199999999999999</v>
@@ -1838,7 +1838,7 @@
         <v>17</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4">
         <v>55</v>
@@ -1847,82 +1847,82 @@
         <v>70</v>
       </c>
       <c r="AK4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL4">
         <v>65</v>
       </c>
       <c r="AM4">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE4">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI4">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4">
         <v>5.6</v>
@@ -1931,7 +1931,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BN4">
         <v>6.4</v>
@@ -1943,37 +1943,37 @@
         <v>27</v>
       </c>
       <c r="BQ4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BR4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS4">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BT4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW4">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BX4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY4">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BZ4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA4">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CB4" t="s">
         <v>220</v>
@@ -2047,7 +2047,7 @@
         <v>1.15</v>
       </c>
       <c r="W5">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="X5">
         <v>29</v>
@@ -2161,61 +2161,61 @@
         <v>1000</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
         <v>1000</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
         <v>1000</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
         <v>1000</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>220</v>
@@ -2247,7 +2247,7 @@
         <v>7.6</v>
       </c>
       <c r="I6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
         <v>3.75</v>
@@ -2403,61 +2403,61 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>220</v>
@@ -2480,19 +2480,19 @@
         <v>179</v>
       </c>
       <c r="F7">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G7">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K7">
         <v>5.1</v>
@@ -2504,55 +2504,55 @@
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O7">
         <v>1.25</v>
       </c>
       <c r="P7">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q7">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R7">
         <v>1.42</v>
       </c>
       <c r="S7">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T7">
         <v>1.92</v>
       </c>
       <c r="U7">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="V7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W7">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="X7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z7">
         <v>85</v>
       </c>
       <c r="AA7">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE7">
         <v>150</v>
@@ -2561,16 +2561,16 @@
         <v>10.5</v>
       </c>
       <c r="AG7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI7">
         <v>130</v>
       </c>
       <c r="AJ7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK7">
         <v>16.5</v>
@@ -2585,115 +2585,115 @@
         <v>7.6</v>
       </c>
       <c r="AO7">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AP7">
+        <v>5</v>
+      </c>
+      <c r="AQ7">
         <v>5.4</v>
       </c>
-      <c r="AQ7">
-        <v>5.7</v>
-      </c>
       <c r="AR7">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS7">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AT7">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AU7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AV7">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AW7">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AY7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AZ7">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BA7">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB7">
+        <v>4.6</v>
+      </c>
+      <c r="BC7">
         <v>4.7</v>
       </c>
-      <c r="BC7">
-        <v>5</v>
-      </c>
       <c r="BD7">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BE7">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF7">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BG7">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH7">
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="G8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H8">
         <v>2.24</v>
@@ -2746,10 +2746,10 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.97</v>
+        <v>3.65</v>
       </c>
       <c r="O8">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P8">
         <v>1.97</v>
@@ -2758,22 +2758,22 @@
         <v>1.83</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S8">
-        <v>1.83</v>
+        <v>2.72</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
         <v>1.64</v>
       </c>
       <c r="W8">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2893,55 +2893,55 @@
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="CB8" t="s">
         <v>220</v>
@@ -2982,7 +2982,7 @@
         <v>4.3</v>
       </c>
       <c r="L9">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
         <v>1.06</v>
@@ -3006,7 +3006,7 @@
         <v>3.15</v>
       </c>
       <c r="T9">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="U9">
         <v>2.04</v>
@@ -3335,7 +3335,7 @@
         <v>13.5</v>
       </c>
       <c r="AW10">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="AX10">
         <v>13.5</v>
@@ -3347,7 +3347,7 @@
         <v>14</v>
       </c>
       <c r="BA10">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BB10">
         <v>6.8</v>
@@ -3371,61 +3371,61 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>220</v>
@@ -4661,19 +4661,19 @@
         <v>1.9</v>
       </c>
       <c r="G16">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H16">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I16">
         <v>4.9</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="K16">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -5142,16 +5142,16 @@
         <v>190</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G18">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H18">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I18">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="J18">
         <v>4.1</v>
@@ -5399,7 +5399,7 @@
         <v>4.2</v>
       </c>
       <c r="K19">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5417,7 +5417,7 @@
         <v>2.22</v>
       </c>
       <c r="Q19">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5871,16 +5871,16 @@
         <v>2.88</v>
       </c>
       <c r="G21">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H21">
         <v>2.26</v>
       </c>
       <c r="I21">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="J21">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K21">
         <v>4.4</v>
@@ -5898,10 +5898,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q21">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6352,22 +6352,22 @@
         <v>195</v>
       </c>
       <c r="F23">
-        <v>1.06</v>
+        <v>3.8</v>
       </c>
       <c r="G23">
-        <v>38</v>
+        <v>3.85</v>
       </c>
       <c r="H23">
-        <v>1.06</v>
+        <v>1.92</v>
       </c>
       <c r="I23">
-        <v>36</v>
+        <v>2.02</v>
       </c>
       <c r="J23">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="K23">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="Q23">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6594,22 +6594,22 @@
         <v>196</v>
       </c>
       <c r="F24">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="G24">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="H24">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="I24">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J24">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K24">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6627,7 +6627,7 @@
         <v>2.14</v>
       </c>
       <c r="Q24">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -7078,22 +7078,22 @@
         <v>198</v>
       </c>
       <c r="F26">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="G26">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H26">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I26">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="J26">
         <v>3.35</v>
       </c>
       <c r="K26">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7323,7 +7323,7 @@
         <v>3.3</v>
       </c>
       <c r="G27">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H27">
         <v>2.4</v>
@@ -7359,16 +7359,16 @@
         <v>1.21</v>
       </c>
       <c r="S27">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="T27">
         <v>2</v>
       </c>
       <c r="U27">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V27">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W27">
         <v>1.37</v>
@@ -7562,16 +7562,16 @@
         <v>200</v>
       </c>
       <c r="F28">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="G28">
         <v>1.9</v>
       </c>
       <c r="H28">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I28">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>3.75</v>
@@ -7592,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q28">
         <v>1.83</v>
@@ -7804,7 +7804,7 @@
         <v>201</v>
       </c>
       <c r="F29">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="G29">
         <v>2.54</v>
@@ -7813,7 +7813,7 @@
         <v>2.94</v>
       </c>
       <c r="I29">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J29">
         <v>3.75</v>
@@ -8157,7 +8157,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ30">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AR30">
         <v>7.4</v>
@@ -8178,19 +8178,19 @@
         <v>7.8</v>
       </c>
       <c r="AX30">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AY30">
         <v>8.6</v>
       </c>
       <c r="AZ30">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA30">
         <v>7.8</v>
       </c>
       <c r="BB30">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BC30">
         <v>13</v>
@@ -8202,7 +8202,7 @@
         <v>7.8</v>
       </c>
       <c r="BF30">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG30">
         <v>7.8</v>
@@ -8297,10 +8297,10 @@
         <v>3</v>
       </c>
       <c r="I31">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J31">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K31">
         <v>3.8</v>
@@ -8563,7 +8563,7 @@
         <v>2.5</v>
       </c>
       <c r="Q32">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R32">
         <v>1.6</v>
@@ -8572,7 +8572,7 @@
         <v>2.34</v>
       </c>
       <c r="T32">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U32">
         <v>2.5</v>
@@ -8617,7 +8617,7 @@
         <v>16.5</v>
       </c>
       <c r="AI32">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ32">
         <v>28</v>
@@ -8641,31 +8641,31 @@
         <v>18.5</v>
       </c>
       <c r="AQ32">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AR32">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS32">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT32">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AU32">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV32">
         <v>12</v>
       </c>
       <c r="AW32">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX32">
         <v>11</v>
       </c>
       <c r="AY32">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ32">
         <v>11.5</v>
@@ -8674,7 +8674,7 @@
         <v>5</v>
       </c>
       <c r="BB32">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BC32">
         <v>13</v>
@@ -8683,7 +8683,7 @@
         <v>19</v>
       </c>
       <c r="BE32">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF32">
         <v>6.4</v>
@@ -9056,7 +9056,7 @@
         <v>0</v>
       </c>
       <c r="T34">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U34">
         <v>2</v>
@@ -9074,7 +9074,7 @@
         <v>10.5</v>
       </c>
       <c r="Z34">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AA34">
         <v>46</v>
@@ -9107,7 +9107,7 @@
         <v>60</v>
       </c>
       <c r="AK34">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL34">
         <v>55</v>
@@ -9143,7 +9143,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW34">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX34">
         <v>14.5</v>
@@ -9155,25 +9155,25 @@
         <v>16</v>
       </c>
       <c r="BA34">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB34">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC34">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD34">
         <v>36</v>
       </c>
       <c r="BE34">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF34">
+        <v>7</v>
+      </c>
+      <c r="BG34">
         <v>6.8</v>
-      </c>
-      <c r="BG34">
-        <v>6.6</v>
       </c>
       <c r="BH34">
         <v>0</v>
@@ -9268,7 +9268,7 @@
         <v>2.4</v>
       </c>
       <c r="J35">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K35">
         <v>3.05</v>
@@ -9519,19 +9519,19 @@
         <v>1.48</v>
       </c>
       <c r="M36">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N36">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O36">
         <v>1.51</v>
       </c>
       <c r="P36">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q36">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R36">
         <v>1.2</v>
@@ -9540,19 +9540,19 @@
         <v>5.1</v>
       </c>
       <c r="T36">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U36">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V36">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W36">
         <v>2.04</v>
       </c>
       <c r="X36">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y36">
         <v>16.5</v>
@@ -9570,7 +9570,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD36">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE36">
         <v>130</v>
@@ -9585,7 +9585,7 @@
         <v>32</v>
       </c>
       <c r="AI36">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ36">
         <v>26</v>
@@ -9597,7 +9597,7 @@
         <v>70</v>
       </c>
       <c r="AM36">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN36">
         <v>25</v>
@@ -9606,7 +9606,7 @@
         <v>220</v>
       </c>
       <c r="AP36">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ36">
         <v>10.5</v>
@@ -9630,7 +9630,7 @@
         <v>4.9</v>
       </c>
       <c r="AX36">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY36">
         <v>9.6</v>
@@ -9639,7 +9639,7 @@
         <v>20</v>
       </c>
       <c r="BA36">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB36">
         <v>18</v>
@@ -9648,7 +9648,7 @@
         <v>21</v>
       </c>
       <c r="BD36">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE36">
         <v>5</v>
@@ -9660,16 +9660,16 @@
         <v>5</v>
       </c>
       <c r="BH36">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI36">
         <v>2.36</v>
       </c>
       <c r="BJ36">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK36">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL36">
         <v>1000</v>
@@ -9693,7 +9693,7 @@
         <v>1000</v>
       </c>
       <c r="BS36">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT36">
         <v>8.800000000000001</v>
@@ -9717,7 +9717,7 @@
         <v>1000</v>
       </c>
       <c r="CA36">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB36" t="s">
         <v>220</v>
@@ -10227,16 +10227,16 @@
         <v>1.5</v>
       </c>
       <c r="G39">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="H39">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I39">
         <v>8</v>
       </c>
       <c r="J39">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K39">
         <v>5.2</v>
@@ -10257,7 +10257,7 @@
         <v>2.18</v>
       </c>
       <c r="Q39">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10950,22 +10950,22 @@
         <v>214</v>
       </c>
       <c r="F42">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G42">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="H42">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I42">
-        <v>1000</v>
+        <v>1.16</v>
       </c>
       <c r="J42">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="K42">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -10980,10 +10980,10 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>1.24</v>
+        <v>2.42</v>
       </c>
       <c r="Q42">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -11198,13 +11198,13 @@
         <v>1.44</v>
       </c>
       <c r="H43">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I43">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J43">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K43">
         <v>5.4</v>
@@ -11676,13 +11676,13 @@
         <v>217</v>
       </c>
       <c r="F45">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G45">
         <v>3.25</v>
       </c>
       <c r="H45">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="I45">
         <v>3.2</v>
@@ -11706,7 +11706,7 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q45">
         <v>2.84</v>
@@ -11918,22 +11918,22 @@
         <v>218</v>
       </c>
       <c r="F46">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="G46">
-        <v>1000</v>
+        <v>1.87</v>
       </c>
       <c r="H46">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I46">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J46">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K46">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -11948,10 +11948,10 @@
         <v>0</v>
       </c>
       <c r="P46">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="Q46">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R46">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-25.xlsx
@@ -1066,7 +1066,7 @@
     <t>Cienciano</t>
   </si>
   <si>
-    <t>2026-07-23 19:04:18</t>
+    <t>2026-07-23 21:17:20</t>
   </si>
 </sst>
 </file>
@@ -1666,7 +1666,7 @@
         <v>2.04</v>
       </c>
       <c r="H2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I2">
         <v>5.9</v>
@@ -1675,7 +1675,7 @@
         <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
         <v>1.67</v>
@@ -1750,7 +1750,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AK2">
         <v>44</v>
@@ -1795,7 +1795,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
         <v>30</v>
@@ -1804,7 +1804,7 @@
         <v>48</v>
       </c>
       <c r="BB2">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BC2">
         <v>21</v>
@@ -1831,55 +1831,55 @@
         <v>14.5</v>
       </c>
       <c r="BK2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO2">
         <v>3.75</v>
       </c>
       <c r="BP2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT2">
         <v>9.199999999999999</v>
       </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
+        <v>10.5</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>11</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
         <v>10</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
-      <c r="BY2">
-        <v>10.5</v>
-      </c>
-      <c r="BZ2">
-        <v>1000</v>
-      </c>
-      <c r="CA2">
-        <v>9.6</v>
       </c>
       <c r="CB2" t="s">
         <v>350</v>
@@ -1911,10 +1911,10 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K3">
         <v>2.92</v>
@@ -1941,7 +1941,7 @@
         <v>1.14</v>
       </c>
       <c r="S3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T3">
         <v>2.32</v>
@@ -1950,7 +1950,7 @@
         <v>1.65</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
         <v>1.47</v>
@@ -2067,13 +2067,13 @@
         <v>2.5</v>
       </c>
       <c r="BI3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BJ3">
         <v>13</v>
       </c>
       <c r="BK3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -2091,19 +2091,19 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT3">
         <v>6.2</v>
       </c>
       <c r="BU3">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BV3">
         <v>34</v>
@@ -2115,13 +2115,13 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="s">
         <v>350</v>
@@ -2144,19 +2144,19 @@
         <v>252</v>
       </c>
       <c r="F4">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="G4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H4">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="I4">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J4">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K4">
         <v>3.65</v>
@@ -2165,25 +2165,25 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P4">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="Q4">
-        <v>2.02</v>
+        <v>1.49</v>
       </c>
       <c r="R4">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="T4">
         <v>1.78</v>
@@ -2192,7 +2192,7 @@
         <v>2.06</v>
       </c>
       <c r="V4">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W4">
         <v>1.4</v>
@@ -2309,7 +2309,7 @@
         <v>3.3</v>
       </c>
       <c r="BI4">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4">
         <v>9.800000000000001</v>
@@ -2643,7 +2643,7 @@
         <v>4.7</v>
       </c>
       <c r="K6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2658,7 +2658,7 @@
         <v>1.21</v>
       </c>
       <c r="P6">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="Q6">
         <v>1.62</v>
@@ -2897,7 +2897,7 @@
         <v>2.98</v>
       </c>
       <c r="O7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P7">
         <v>1.67</v>
@@ -2906,7 +2906,7 @@
         <v>2.26</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S7">
         <v>4.4</v>
@@ -3121,10 +3121,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J8">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K8">
         <v>5.1</v>
@@ -3220,7 +3220,7 @@
         <v>180</v>
       </c>
       <c r="AP8">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="AQ8">
         <v>7.2</v>
@@ -3357,10 +3357,10 @@
         <v>2.96</v>
       </c>
       <c r="G9">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="H9">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="I9">
         <v>2.54</v>
@@ -3369,7 +3369,7 @@
         <v>3.5</v>
       </c>
       <c r="K9">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -3378,13 +3378,13 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O9">
         <v>1.28</v>
       </c>
       <c r="P9">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="Q9">
         <v>1.84</v>
@@ -3393,7 +3393,7 @@
         <v>1.35</v>
       </c>
       <c r="S9">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -3402,10 +3402,10 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W9">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3596,22 +3596,22 @@
         <v>258</v>
       </c>
       <c r="F10">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="G10">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="H10">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="I10">
-        <v>870</v>
+        <v>15</v>
       </c>
       <c r="J10">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3838,16 +3838,16 @@
         <v>259</v>
       </c>
       <c r="F11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="G11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>1.67</v>
       </c>
       <c r="I11">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="J11">
         <v>4.1</v>
@@ -3862,7 +3862,7 @@
         <v>1.06</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O11">
         <v>1.29</v>
@@ -3877,7 +3877,7 @@
         <v>1.41</v>
       </c>
       <c r="S11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T11">
         <v>1.87</v>
@@ -4009,7 +4009,7 @@
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -4018,7 +4018,7 @@
         <v>13.5</v>
       </c>
       <c r="BN11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BO11">
         <v>6.6</v>
@@ -4027,19 +4027,19 @@
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT11">
         <v>4.3</v>
       </c>
       <c r="BU11">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="BV11">
         <v>11.5</v>
@@ -4051,13 +4051,13 @@
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB11" t="s">
         <v>350</v>
@@ -4086,10 +4086,10 @@
         <v>2.12</v>
       </c>
       <c r="H12">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I12">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J12">
         <v>3.9</v>
@@ -4119,7 +4119,7 @@
         <v>1.54</v>
       </c>
       <c r="S12">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T12">
         <v>1.63</v>
@@ -4128,10 +4128,10 @@
         <v>2.44</v>
       </c>
       <c r="V12">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X12">
         <v>24</v>
@@ -4331,7 +4331,7 @@
         <v>2.6</v>
       </c>
       <c r="I13">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="J13">
         <v>3.35</v>
@@ -4352,13 +4352,13 @@
         <v>1.33</v>
       </c>
       <c r="P13">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q13">
         <v>1.94</v>
       </c>
       <c r="R13">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S13">
         <v>3.5</v>
@@ -4370,7 +4370,7 @@
         <v>2.14</v>
       </c>
       <c r="V13">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W13">
         <v>1.48</v>
@@ -4573,13 +4573,13 @@
         <v>2.44</v>
       </c>
       <c r="I14">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J14">
         <v>3.4</v>
       </c>
       <c r="K14">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L14">
         <v>1.36</v>
@@ -4588,13 +4588,13 @@
         <v>1.07</v>
       </c>
       <c r="N14">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O14">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P14">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q14">
         <v>1.96</v>
@@ -4612,10 +4612,10 @@
         <v>2.2</v>
       </c>
       <c r="V14">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X14">
         <v>14.5</v>
@@ -4624,7 +4624,7 @@
         <v>11</v>
       </c>
       <c r="Z14">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA14">
         <v>36</v>
@@ -4633,7 +4633,7 @@
         <v>13</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD14">
         <v>12</v>
@@ -4654,7 +4654,7 @@
         <v>42</v>
       </c>
       <c r="AJ14">
-        <v>55</v>
+        <v>240</v>
       </c>
       <c r="AK14">
         <v>36</v>
@@ -4663,25 +4663,25 @@
         <v>46</v>
       </c>
       <c r="AM14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
         <v>34</v>
       </c>
       <c r="AO14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP14">
         <v>13</v>
       </c>
       <c r="AQ14">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR14">
         <v>14.5</v>
       </c>
       <c r="AS14">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AT14">
         <v>11</v>
@@ -4693,10 +4693,10 @@
         <v>10.5</v>
       </c>
       <c r="AW14">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AX14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY14">
         <v>12</v>
@@ -4705,22 +4705,22 @@
         <v>15</v>
       </c>
       <c r="BA14">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="BB14">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BC14">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="BD14">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="BE14">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BF14">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BG14">
         <v>18.5</v>
@@ -4735,16 +4735,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK14">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO14">
         <v>4.9</v>
@@ -4753,13 +4753,13 @@
         <v>25</v>
       </c>
       <c r="BQ14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR14">
         <v>38</v>
       </c>
       <c r="BS14">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT14">
         <v>5.7</v>
@@ -4768,22 +4768,22 @@
         <v>4.3</v>
       </c>
       <c r="BV14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW14">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX14">
         <v>34</v>
       </c>
       <c r="BY14">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ14">
         <v>28</v>
       </c>
       <c r="CA14">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB14" t="s">
         <v>350</v>
@@ -4815,13 +4815,13 @@
         <v>2.48</v>
       </c>
       <c r="I15">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K15">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4839,7 +4839,7 @@
         <v>1.61</v>
       </c>
       <c r="Q15">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R15">
         <v>1.24</v>
@@ -5054,7 +5054,7 @@
         <v>3.9</v>
       </c>
       <c r="H16">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I16">
         <v>2.36</v>
@@ -5063,7 +5063,7 @@
         <v>3.4</v>
       </c>
       <c r="K16">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L16">
         <v>1.29</v>
@@ -5072,7 +5072,7 @@
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O16">
         <v>1.29</v>
@@ -5081,10 +5081,10 @@
         <v>1.94</v>
       </c>
       <c r="Q16">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R16">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S16">
         <v>2.28</v>
@@ -5290,13 +5290,13 @@
         <v>265</v>
       </c>
       <c r="F17">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G17">
         <v>3</v>
       </c>
       <c r="H17">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I17">
         <v>2.96</v>
@@ -5320,19 +5320,19 @@
         <v>1.33</v>
       </c>
       <c r="P17">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q17">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R17">
         <v>1.34</v>
       </c>
       <c r="S17">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T17">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U17">
         <v>2.12</v>
@@ -5452,22 +5452,22 @@
         <v>19</v>
       </c>
       <c r="BH17">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BI17">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BJ17">
         <v>9.6</v>
       </c>
       <c r="BK17">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN17">
         <v>6</v>
@@ -5479,31 +5479,31 @@
         <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BR17">
         <v>1000</v>
       </c>
       <c r="BS17">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT17">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU17">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ17">
         <v>0</v>
@@ -5532,7 +5532,7 @@
         <v>266</v>
       </c>
       <c r="F18">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G18">
         <v>2.5</v>
@@ -5562,10 +5562,10 @@
         <v>1.38</v>
       </c>
       <c r="P18">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q18">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R18">
         <v>1.29</v>
@@ -5580,7 +5580,7 @@
         <v>2.02</v>
       </c>
       <c r="V18">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
         <v>1.66</v>
@@ -5694,10 +5694,10 @@
         <v>5.1</v>
       </c>
       <c r="BH18">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI18">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ18">
         <v>10</v>
@@ -5709,7 +5709,7 @@
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN18">
         <v>5.2</v>
@@ -5721,13 +5721,13 @@
         <v>26</v>
       </c>
       <c r="BQ18">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT18">
         <v>6.6</v>
@@ -5739,13 +5739,13 @@
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX18">
         <v>60</v>
       </c>
       <c r="BY18">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ18">
         <v>0</v>
@@ -5774,7 +5774,7 @@
         <v>267</v>
       </c>
       <c r="F19">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G19">
         <v>2.04</v>
@@ -5786,7 +5786,7 @@
         <v>4.2</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K19">
         <v>4.8</v>
@@ -5804,7 +5804,7 @@
         <v>1.16</v>
       </c>
       <c r="P19">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q19">
         <v>1.5</v>
@@ -5813,10 +5813,10 @@
         <v>1.66</v>
       </c>
       <c r="S19">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T19">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U19">
         <v>2.58</v>
@@ -5825,7 +5825,7 @@
         <v>1.31</v>
       </c>
       <c r="W19">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X19">
         <v>34</v>
@@ -5942,34 +5942,34 @@
         <v>3.75</v>
       </c>
       <c r="BJ19">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN19">
         <v>5.4</v>
       </c>
       <c r="BO19">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ19">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR19">
         <v>21</v>
       </c>
       <c r="BS19">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT19">
         <v>8</v>
@@ -5981,19 +5981,19 @@
         <v>27</v>
       </c>
       <c r="BW19">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY19">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ19">
         <v>14</v>
       </c>
       <c r="CA19">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB19" t="s">
         <v>350</v>
@@ -6025,10 +6025,10 @@
         <v>2.86</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J20">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <v>4.3</v>
@@ -6040,28 +6040,28 @@
         <v>1.02</v>
       </c>
       <c r="N20">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O20">
         <v>1.15</v>
       </c>
       <c r="P20">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q20">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R20">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="S20">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T20">
         <v>1.44</v>
       </c>
       <c r="U20">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V20">
         <v>1.5</v>
@@ -6070,7 +6070,7 @@
         <v>1.71</v>
       </c>
       <c r="X20">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="Y20">
         <v>22</v>
@@ -6079,13 +6079,13 @@
         <v>28</v>
       </c>
       <c r="AA20">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="AB20">
         <v>19.5</v>
       </c>
       <c r="AC20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD20">
         <v>14.5</v>
@@ -6094,58 +6094,58 @@
         <v>27</v>
       </c>
       <c r="AF20">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG20">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH20">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI20">
         <v>29</v>
       </c>
       <c r="AJ20">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AK20">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL20">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM20">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AN20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO20">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP20">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="AQ20">
+        <v>18.5</v>
+      </c>
+      <c r="AR20">
+        <v>18</v>
+      </c>
+      <c r="AS20">
+        <v>36</v>
+      </c>
+      <c r="AT20">
+        <v>16.5</v>
+      </c>
+      <c r="AU20">
+        <v>9.6</v>
+      </c>
+      <c r="AV20">
+        <v>12</v>
+      </c>
+      <c r="AW20">
         <v>17.5</v>
-      </c>
-      <c r="AR20">
-        <v>19</v>
-      </c>
-      <c r="AS20">
-        <v>34</v>
-      </c>
-      <c r="AT20">
-        <v>16</v>
-      </c>
-      <c r="AU20">
-        <v>9.4</v>
-      </c>
-      <c r="AV20">
-        <v>11.5</v>
-      </c>
-      <c r="AW20">
-        <v>19</v>
       </c>
       <c r="AX20">
         <v>18</v>
@@ -6157,25 +6157,25 @@
         <v>12</v>
       </c>
       <c r="BA20">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BB20">
-        <v>6.8</v>
+        <v>29</v>
       </c>
       <c r="BC20">
         <v>18</v>
       </c>
       <c r="BD20">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BE20">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BF20">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -6261,7 +6261,7 @@
         <v>2.12</v>
       </c>
       <c r="G21">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H21">
         <v>3.35</v>
@@ -6285,13 +6285,13 @@
         <v>4.4</v>
       </c>
       <c r="O21">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P21">
         <v>2.18</v>
       </c>
       <c r="Q21">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R21">
         <v>1.47</v>
@@ -6300,7 +6300,7 @@
         <v>2.78</v>
       </c>
       <c r="T21">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U21">
         <v>2.34</v>
@@ -6309,7 +6309,7 @@
         <v>1.35</v>
       </c>
       <c r="W21">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X21">
         <v>23</v>
@@ -6324,7 +6324,7 @@
         <v>60</v>
       </c>
       <c r="AB21">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC21">
         <v>9.199999999999999</v>
@@ -6336,7 +6336,7 @@
         <v>38</v>
       </c>
       <c r="AF21">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AG21">
         <v>11.5</v>
@@ -6375,7 +6375,7 @@
         <v>22</v>
       </c>
       <c r="AS21">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT21">
         <v>10.5</v>
@@ -6411,7 +6411,7 @@
         <v>23</v>
       </c>
       <c r="BE21">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF21">
         <v>11.5</v>
@@ -6500,16 +6500,16 @@
         <v>270</v>
       </c>
       <c r="F22">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="G22">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="H22">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I22">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="J22">
         <v>3.35</v>
@@ -6524,7 +6524,7 @@
         <v>1.07</v>
       </c>
       <c r="N22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O22">
         <v>1.33</v>
@@ -6533,25 +6533,25 @@
         <v>1.87</v>
       </c>
       <c r="Q22">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="R22">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S22">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T22">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U22">
         <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W22">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="X22">
         <v>14.5</v>
@@ -6563,7 +6563,7 @@
         <v>28</v>
       </c>
       <c r="AA22">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB22">
         <v>10.5</v>
@@ -6581,7 +6581,7 @@
         <v>16</v>
       </c>
       <c r="AG22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH22">
         <v>18</v>
@@ -6602,10 +6602,10 @@
         <v>120</v>
       </c>
       <c r="AN22">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO22">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AP22">
         <v>12</v>
@@ -6617,7 +6617,7 @@
         <v>20</v>
       </c>
       <c r="AS22">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT22">
         <v>8.800000000000001</v>
@@ -6632,7 +6632,7 @@
         <v>5.6</v>
       </c>
       <c r="AX22">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY22">
         <v>10</v>
@@ -6656,10 +6656,10 @@
         <v>6</v>
       </c>
       <c r="BF22">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BG22">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6760,7 +6760,7 @@
         <v>4.3</v>
       </c>
       <c r="L23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M23">
         <v>1.05</v>
@@ -6922,10 +6922,10 @@
         <v>21</v>
       </c>
       <c r="BN23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO23">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP23">
         <v>18.5</v>
@@ -6937,7 +6937,7 @@
         <v>34</v>
       </c>
       <c r="BS23">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BT23">
         <v>11</v>
@@ -6949,19 +6949,19 @@
         <v>46</v>
       </c>
       <c r="BW23">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY23">
         <v>21</v>
       </c>
       <c r="BZ23">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="CA23">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB23" t="s">
         <v>350</v>
@@ -7011,13 +7011,13 @@
         <v>7</v>
       </c>
       <c r="O24">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P24">
         <v>3.05</v>
       </c>
       <c r="Q24">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R24">
         <v>1.84</v>
@@ -7035,7 +7035,7 @@
         <v>2.56</v>
       </c>
       <c r="W24">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X24">
         <v>48</v>
@@ -7086,7 +7086,7 @@
         <v>70</v>
       </c>
       <c r="AN24">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO24">
         <v>5.8</v>
@@ -7122,13 +7122,13 @@
         <v>16.5</v>
       </c>
       <c r="AZ24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA24">
         <v>16.5</v>
       </c>
       <c r="BB24">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC24">
         <v>4.1</v>
@@ -7256,10 +7256,10 @@
         <v>1.32</v>
       </c>
       <c r="P25">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q25">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R25">
         <v>1.27</v>
@@ -7295,7 +7295,7 @@
         <v>1000</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD25">
         <v>1000</v>
@@ -7334,58 +7334,58 @@
         <v>1000</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AU25">
         <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BH25">
         <v>1000</v>
@@ -7471,7 +7471,7 @@
         <v>2.06</v>
       </c>
       <c r="G26">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H26">
         <v>3.2</v>
@@ -7519,13 +7519,13 @@
         <v>1.37</v>
       </c>
       <c r="W26">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X26">
         <v>25</v>
       </c>
       <c r="Y26">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z26">
         <v>32</v>
@@ -7546,7 +7546,7 @@
         <v>38</v>
       </c>
       <c r="AF26">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG26">
         <v>13</v>
@@ -7555,7 +7555,7 @@
         <v>17</v>
       </c>
       <c r="AI26">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ26">
         <v>32</v>
@@ -7564,7 +7564,7 @@
         <v>24</v>
       </c>
       <c r="AL26">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM26">
         <v>80</v>
@@ -7639,16 +7639,16 @@
         <v>12</v>
       </c>
       <c r="BK26">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BN26">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BO26">
         <v>3.7</v>
@@ -7657,37 +7657,37 @@
         <v>20</v>
       </c>
       <c r="BQ26">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BR26">
         <v>34</v>
       </c>
       <c r="BS26">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BT26">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BU26">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV26">
         <v>34</v>
       </c>
       <c r="BW26">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BX26">
         <v>44</v>
       </c>
       <c r="BY26">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BZ26">
         <v>25</v>
       </c>
       <c r="CA26">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CB26" t="s">
         <v>350</v>
@@ -7722,7 +7722,7 @@
         <v>990</v>
       </c>
       <c r="J27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K27">
         <v>950</v>
@@ -7952,19 +7952,19 @@
         <v>276</v>
       </c>
       <c r="F28">
-        <v>1.45</v>
+        <v>1.06</v>
       </c>
       <c r="G28">
         <v>990</v>
       </c>
       <c r="H28">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="I28">
         <v>1000</v>
       </c>
       <c r="J28">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K28">
         <v>3.3</v>
@@ -8224,10 +8224,10 @@
         <v>1.26</v>
       </c>
       <c r="P29">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q29">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R29">
         <v>1.46</v>
@@ -8269,7 +8269,7 @@
         <v>10.5</v>
       </c>
       <c r="AE29">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AF29">
         <v>46</v>
@@ -8290,13 +8290,13 @@
         <v>60</v>
       </c>
       <c r="AL29">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM29">
         <v>100</v>
       </c>
       <c r="AN29">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO29">
         <v>10.5</v>
@@ -8317,7 +8317,7 @@
         <v>17.5</v>
       </c>
       <c r="AU29">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV29">
         <v>9.199999999999999</v>
@@ -8341,10 +8341,10 @@
         <v>12.5</v>
       </c>
       <c r="BC29">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="BD29">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BE29">
         <v>70</v>
@@ -8359,19 +8359,19 @@
         <v>1000</v>
       </c>
       <c r="BI29">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BJ29">
         <v>13.5</v>
       </c>
       <c r="BK29">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="BN29">
         <v>11.5</v>
@@ -8383,13 +8383,13 @@
         <v>1000</v>
       </c>
       <c r="BQ29">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="BR29">
         <v>1000</v>
       </c>
       <c r="BS29">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BT29">
         <v>6.4</v>
@@ -8398,22 +8398,22 @@
         <v>3.1</v>
       </c>
       <c r="BV29">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BW29">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="BX29">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY29">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BZ29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA29">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CB29" t="s">
         <v>350</v>
@@ -8457,7 +8457,7 @@
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N30">
         <v>5.2</v>
@@ -8466,7 +8466,7 @@
         <v>1.21</v>
       </c>
       <c r="P30">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q30">
         <v>1.63</v>
@@ -8475,7 +8475,7 @@
         <v>1.56</v>
       </c>
       <c r="S30">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="T30">
         <v>1.54</v>
@@ -8487,7 +8487,7 @@
         <v>1.45</v>
       </c>
       <c r="W30">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X30">
         <v>27</v>
@@ -8541,7 +8541,7 @@
         <v>14</v>
       </c>
       <c r="AO30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP30">
         <v>19</v>
@@ -8577,7 +8577,7 @@
         <v>12.5</v>
       </c>
       <c r="BA30">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB30">
         <v>5.4</v>
@@ -8589,7 +8589,7 @@
         <v>5.4</v>
       </c>
       <c r="BE30">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF30">
         <v>10.5</v>
@@ -8607,7 +8607,7 @@
         <v>11.5</v>
       </c>
       <c r="BK30">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL30">
         <v>1000</v>
@@ -8684,7 +8684,7 @@
         <v>6.2</v>
       </c>
       <c r="H31">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I31">
         <v>1.7</v>
@@ -8813,7 +8813,7 @@
         <v>8.6</v>
       </c>
       <c r="AY31">
-        <v>19.5</v>
+        <v>7.2</v>
       </c>
       <c r="AZ31">
         <v>17</v>
@@ -8929,7 +8929,7 @@
         <v>1.82</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J32">
         <v>3.55</v>
@@ -8944,7 +8944,7 @@
         <v>1.05</v>
       </c>
       <c r="N32">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="O32">
         <v>1.25</v>
@@ -8962,7 +8962,7 @@
         <v>2.66</v>
       </c>
       <c r="T32">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U32">
         <v>1.94</v>
@@ -9174,7 +9174,7 @@
         <v>2.54</v>
       </c>
       <c r="J33">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K33">
         <v>4.4</v>
@@ -9198,10 +9198,10 @@
         <v>1.51</v>
       </c>
       <c r="R33">
-        <v>1.51</v>
+        <v>1.05</v>
       </c>
       <c r="S33">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="T33">
         <v>1.11</v>
@@ -9404,13 +9404,13 @@
         <v>282</v>
       </c>
       <c r="F34">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G34">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H34">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="I34">
         <v>2.56</v>
@@ -9419,7 +9419,7 @@
         <v>3.6</v>
       </c>
       <c r="K34">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -9449,7 +9449,7 @@
         <v>1.62</v>
       </c>
       <c r="U34">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V34">
         <v>1.64</v>
@@ -9467,7 +9467,7 @@
         <v>19.5</v>
       </c>
       <c r="AA34">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB34">
         <v>15</v>
@@ -9524,7 +9524,7 @@
         <v>6.4</v>
       </c>
       <c r="AT34">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU34">
         <v>7.4</v>
@@ -9545,7 +9545,7 @@
         <v>12</v>
       </c>
       <c r="BA34">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB34">
         <v>6.6</v>
@@ -9658,7 +9658,7 @@
         <v>990</v>
       </c>
       <c r="J35">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K35">
         <v>950</v>
@@ -10498,7 +10498,7 @@
         <v>7.6</v>
       </c>
       <c r="AV38">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW38">
         <v>7.6</v>
@@ -10614,10 +10614,10 @@
         <v>287</v>
       </c>
       <c r="F39">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G39">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="H39">
         <v>5.6</v>
@@ -10632,7 +10632,7 @@
         <v>4.8</v>
       </c>
       <c r="L39">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M39">
         <v>1.04</v>
@@ -10641,22 +10641,22 @@
         <v>4.8</v>
       </c>
       <c r="O39">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P39">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q39">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R39">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S39">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T39">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U39">
         <v>2.16</v>
@@ -10665,7 +10665,7 @@
         <v>1.18</v>
       </c>
       <c r="W39">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X39">
         <v>26</v>
@@ -10677,7 +10677,7 @@
         <v>60</v>
       </c>
       <c r="AA39">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB39">
         <v>10.5</v>
@@ -10692,7 +10692,7 @@
         <v>90</v>
       </c>
       <c r="AF39">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG39">
         <v>10.5</v>
@@ -10707,7 +10707,7 @@
         <v>23</v>
       </c>
       <c r="AK39">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AL39">
         <v>46</v>
@@ -10728,22 +10728,22 @@
         <v>20</v>
       </c>
       <c r="AR39">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS39">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AT39">
         <v>9.199999999999999</v>
       </c>
       <c r="AU39">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV39">
         <v>16.5</v>
       </c>
       <c r="AW39">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AX39">
         <v>8.199999999999999</v>
@@ -10755,7 +10755,7 @@
         <v>14</v>
       </c>
       <c r="BA39">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB39">
         <v>11.5</v>
@@ -10767,13 +10767,13 @@
         <v>21</v>
       </c>
       <c r="BE39">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BF39">
         <v>6.6</v>
       </c>
       <c r="BG39">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH39">
         <v>1000</v>
@@ -10856,7 +10856,7 @@
         <v>288</v>
       </c>
       <c r="F40">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G40">
         <v>2.4</v>
@@ -11098,7 +11098,7 @@
         <v>289</v>
       </c>
       <c r="F41">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G41">
         <v>2.6</v>
@@ -11113,7 +11113,7 @@
         <v>3.25</v>
       </c>
       <c r="K41">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="L41">
         <v>1.01</v>
@@ -11143,7 +11143,7 @@
         <v>1.76</v>
       </c>
       <c r="U41">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V41">
         <v>1.4</v>
@@ -11600,7 +11600,7 @@
         <v>3.6</v>
       </c>
       <c r="L43">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M43">
         <v>1.08</v>
@@ -11618,7 +11618,7 @@
         <v>2.08</v>
       </c>
       <c r="R43">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S43">
         <v>3.85</v>
@@ -11651,7 +11651,7 @@
         <v>14</v>
       </c>
       <c r="AC43">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD43">
         <v>12.5</v>
@@ -11699,7 +11699,7 @@
         <v>12</v>
       </c>
       <c r="AS43">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT43">
         <v>10</v>
@@ -11711,7 +11711,7 @@
         <v>9.6</v>
       </c>
       <c r="AW43">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX43">
         <v>21</v>
@@ -11723,22 +11723,22 @@
         <v>16</v>
       </c>
       <c r="BA43">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BB43">
         <v>6</v>
       </c>
       <c r="BC43">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD43">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE43">
         <v>6.2</v>
       </c>
       <c r="BF43">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG43">
         <v>17</v>
@@ -11753,7 +11753,7 @@
         <v>10.5</v>
       </c>
       <c r="BK43">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BL43">
         <v>1000</v>
@@ -11765,7 +11765,7 @@
         <v>7</v>
       </c>
       <c r="BO43">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BP43">
         <v>32</v>
@@ -11783,7 +11783,7 @@
         <v>5.2</v>
       </c>
       <c r="BU43">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BV43">
         <v>18.5</v>
@@ -11836,7 +11836,7 @@
         <v>1000</v>
       </c>
       <c r="J44">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K44">
         <v>950</v>
@@ -12066,10 +12066,10 @@
         <v>293</v>
       </c>
       <c r="F45">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="G45">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H45">
         <v>3.3</v>
@@ -12078,10 +12078,10 @@
         <v>4.4</v>
       </c>
       <c r="J45">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K45">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="L45">
         <v>1.01</v>
@@ -12102,7 +12102,7 @@
         <v>1.96</v>
       </c>
       <c r="R45">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S45">
         <v>3.1</v>
@@ -12117,7 +12117,7 @@
         <v>1.29</v>
       </c>
       <c r="W45">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X45">
         <v>1000</v>
@@ -12308,19 +12308,19 @@
         <v>294</v>
       </c>
       <c r="F46">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G46">
         <v>990</v>
       </c>
       <c r="H46">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I46">
         <v>990</v>
       </c>
       <c r="J46">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K46">
         <v>950</v>
@@ -12562,7 +12562,7 @@
         <v>990</v>
       </c>
       <c r="J47">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K47">
         <v>950</v>
@@ -12586,7 +12586,7 @@
         <v>1.23</v>
       </c>
       <c r="R47">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S47">
         <v>1.23</v>
@@ -12792,7 +12792,7 @@
         <v>296</v>
       </c>
       <c r="F48">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="G48">
         <v>990</v>
@@ -12804,7 +12804,7 @@
         <v>990</v>
       </c>
       <c r="J48">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K48">
         <v>950</v>
@@ -13076,7 +13076,7 @@
         <v>3.1</v>
       </c>
       <c r="T49">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U49">
         <v>1.86</v>
@@ -13279,7 +13279,7 @@
         <v>2.44</v>
       </c>
       <c r="G50">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H50">
         <v>3.05</v>
@@ -13306,7 +13306,7 @@
         <v>1.29</v>
       </c>
       <c r="P50">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q50">
         <v>1.83</v>
@@ -13339,7 +13339,7 @@
         <v>27</v>
       </c>
       <c r="AA50">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB50">
         <v>14</v>
@@ -13357,7 +13357,7 @@
         <v>21</v>
       </c>
       <c r="AG50">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH50">
         <v>20</v>
@@ -13393,7 +13393,7 @@
         <v>19</v>
       </c>
       <c r="AS50">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT50">
         <v>9.800000000000001</v>
@@ -13405,7 +13405,7 @@
         <v>11.5</v>
       </c>
       <c r="AW50">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX50">
         <v>14</v>
@@ -13417,19 +13417,19 @@
         <v>14</v>
       </c>
       <c r="BA50">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB50">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC50">
         <v>21</v>
       </c>
       <c r="BD50">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE50">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF50">
         <v>13.5</v>
@@ -13453,13 +13453,13 @@
         <v>1000</v>
       </c>
       <c r="BM50">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="BN50">
         <v>7.8</v>
       </c>
       <c r="BO50">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP50">
         <v>25</v>
@@ -13477,7 +13477,7 @@
         <v>9</v>
       </c>
       <c r="BU50">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV50">
         <v>34</v>
@@ -13486,7 +13486,7 @@
         <v>1.75</v>
       </c>
       <c r="BX50">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY50">
         <v>1.78</v>
@@ -13578,7 +13578,7 @@
         <v>19</v>
       </c>
       <c r="Z51">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA51">
         <v>140</v>
@@ -13772,7 +13772,7 @@
         <v>990</v>
       </c>
       <c r="J52">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K52">
         <v>950</v>
@@ -14167,19 +14167,19 @@
         <v>1000</v>
       </c>
       <c r="BI53">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BJ53">
         <v>17</v>
       </c>
       <c r="BK53">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BL53">
         <v>1000</v>
       </c>
       <c r="BM53">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BN53">
         <v>5</v>
@@ -14191,37 +14191,37 @@
         <v>12.5</v>
       </c>
       <c r="BQ53">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BR53">
         <v>38</v>
       </c>
       <c r="BS53">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BT53">
         <v>17</v>
       </c>
       <c r="BU53">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BV53">
         <v>1000</v>
       </c>
       <c r="BW53">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BX53">
         <v>1000</v>
       </c>
       <c r="BY53">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BZ53">
         <v>25</v>
       </c>
       <c r="CA53">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="CB53" t="s">
         <v>350</v>
@@ -14247,10 +14247,10 @@
         <v>2.44</v>
       </c>
       <c r="G54">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H54">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I54">
         <v>3.05</v>
@@ -14280,7 +14280,7 @@
         <v>1.72</v>
       </c>
       <c r="R54">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S54">
         <v>2.76</v>
@@ -14289,13 +14289,13 @@
         <v>1.62</v>
       </c>
       <c r="U54">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="V54">
         <v>1.48</v>
       </c>
       <c r="W54">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X54">
         <v>18.5</v>
@@ -14409,19 +14409,19 @@
         <v>1000</v>
       </c>
       <c r="BI54">
-        <v>2.78</v>
+        <v>1.95</v>
       </c>
       <c r="BJ54">
         <v>12.5</v>
       </c>
       <c r="BK54">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BL54">
         <v>1000</v>
       </c>
       <c r="BM54">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BN54">
         <v>7.6</v>
@@ -14433,13 +14433,13 @@
         <v>23</v>
       </c>
       <c r="BQ54">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BR54">
         <v>36</v>
       </c>
       <c r="BS54">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BT54">
         <v>8.800000000000001</v>
@@ -14451,19 +14451,19 @@
         <v>30</v>
       </c>
       <c r="BW54">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="BX54">
         <v>44</v>
       </c>
       <c r="BY54">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BZ54">
         <v>28</v>
       </c>
       <c r="CA54">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="CB54" t="s">
         <v>350</v>
@@ -14489,7 +14489,7 @@
         <v>1.94</v>
       </c>
       <c r="G55">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H55">
         <v>3.65</v>
@@ -14534,19 +14534,19 @@
         <v>2.5</v>
       </c>
       <c r="V55">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W55">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X55">
         <v>32</v>
       </c>
       <c r="Y55">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z55">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA55">
         <v>70</v>
@@ -14561,7 +14561,7 @@
         <v>17</v>
       </c>
       <c r="AE55">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF55">
         <v>16</v>
@@ -14600,10 +14600,10 @@
         <v>17</v>
       </c>
       <c r="AR55">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS55">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT55">
         <v>11.5</v>
@@ -14615,7 +14615,7 @@
         <v>13.5</v>
       </c>
       <c r="AW55">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX55">
         <v>13</v>
@@ -14627,7 +14627,7 @@
         <v>13</v>
       </c>
       <c r="BA55">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB55">
         <v>19.5</v>
@@ -14636,10 +14636,10 @@
         <v>15.5</v>
       </c>
       <c r="BD55">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE55">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF55">
         <v>7.6</v>
@@ -14654,37 +14654,37 @@
         <v>3.45</v>
       </c>
       <c r="BJ55">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK55">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL55">
         <v>1000</v>
       </c>
       <c r="BM55">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN55">
         <v>5.4</v>
       </c>
       <c r="BO55">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP55">
         <v>13.5</v>
       </c>
       <c r="BQ55">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR55">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BS55">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BT55">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU55">
         <v>5.7</v>
@@ -14693,19 +14693,19 @@
         <v>28</v>
       </c>
       <c r="BW55">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX55">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY55">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ55">
         <v>15.5</v>
       </c>
       <c r="CA55">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB55" t="s">
         <v>350</v>
@@ -14797,7 +14797,7 @@
         <v>17.5</v>
       </c>
       <c r="AC56">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD56">
         <v>34</v>
@@ -14827,7 +14827,7 @@
         <v>25</v>
       </c>
       <c r="AM56">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN56">
         <v>3.6</v>
@@ -14836,16 +14836,16 @@
         <v>60</v>
       </c>
       <c r="AP56">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ56">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR56">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS56">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT56">
         <v>14.5</v>
@@ -14854,10 +14854,10 @@
         <v>13</v>
       </c>
       <c r="AV56">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AW56">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX56">
         <v>11</v>
@@ -14869,7 +14869,7 @@
         <v>19</v>
       </c>
       <c r="BA56">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB56">
         <v>13</v>
@@ -14970,7 +14970,7 @@
         <v>305</v>
       </c>
       <c r="F57">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G57">
         <v>2.6</v>
@@ -14988,7 +14988,7 @@
         <v>3.8</v>
       </c>
       <c r="L57">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M57">
         <v>1.07</v>
@@ -15006,7 +15006,7 @@
         <v>1.87</v>
       </c>
       <c r="R57">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S57">
         <v>3.25</v>
@@ -15212,10 +15212,10 @@
         <v>306</v>
       </c>
       <c r="F58">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G58">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H58">
         <v>6.8</v>
@@ -15230,7 +15230,7 @@
         <v>4.4</v>
       </c>
       <c r="L58">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M58">
         <v>1.07</v>
@@ -15242,7 +15242,7 @@
         <v>1.34</v>
       </c>
       <c r="P58">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q58">
         <v>2</v>
@@ -15263,7 +15263,7 @@
         <v>1.14</v>
       </c>
       <c r="W58">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="X58">
         <v>14.5</v>
@@ -15275,7 +15275,7 @@
         <v>65</v>
       </c>
       <c r="AA58">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB58">
         <v>7.6</v>
@@ -15287,7 +15287,7 @@
         <v>30</v>
       </c>
       <c r="AE58">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF58">
         <v>10</v>
@@ -15317,13 +15317,13 @@
         <v>11.5</v>
       </c>
       <c r="AO58">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP58">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="AQ58">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR58">
         <v>6.4</v>
@@ -15338,7 +15338,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV58">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AW58">
         <v>6.8</v>
@@ -15356,16 +15356,16 @@
         <v>6.8</v>
       </c>
       <c r="BB58">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="BC58">
-        <v>5.4</v>
+        <v>15.5</v>
       </c>
       <c r="BD58">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BE58">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF58">
         <v>8</v>
@@ -15454,7 +15454,7 @@
         <v>307</v>
       </c>
       <c r="F59">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G59">
         <v>4.3</v>
@@ -15463,13 +15463,13 @@
         <v>2.04</v>
       </c>
       <c r="I59">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="J59">
         <v>3.4</v>
       </c>
       <c r="K59">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L59">
         <v>1.01</v>
@@ -15481,10 +15481,10 @@
         <v>3.7</v>
       </c>
       <c r="O59">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P59">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q59">
         <v>1.87</v>
@@ -15502,7 +15502,7 @@
         <v>1.11</v>
       </c>
       <c r="V59">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W59">
         <v>1.3</v>
@@ -15511,7 +15511,7 @@
         <v>1000</v>
       </c>
       <c r="Y59">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z59">
         <v>1000</v>
@@ -15520,7 +15520,7 @@
         <v>1000</v>
       </c>
       <c r="AB59">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC59">
         <v>1000</v>
@@ -15625,55 +15625,55 @@
         <v>1000</v>
       </c>
       <c r="BK59">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BL59">
         <v>1000</v>
       </c>
       <c r="BM59">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BN59">
         <v>1000</v>
       </c>
       <c r="BO59">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BP59">
         <v>1000</v>
       </c>
       <c r="BQ59">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BR59">
         <v>1000</v>
       </c>
       <c r="BS59">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BT59">
         <v>1000</v>
       </c>
       <c r="BU59">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BV59">
         <v>1000</v>
       </c>
       <c r="BW59">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BX59">
         <v>1000</v>
       </c>
       <c r="BY59">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BZ59">
         <v>1000</v>
       </c>
       <c r="CA59">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="CB59" t="s">
         <v>350</v>
@@ -15699,13 +15699,13 @@
         <v>1.86</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H60">
         <v>3.9</v>
       </c>
       <c r="I60">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J60">
         <v>4</v>
@@ -15792,7 +15792,7 @@
         <v>23</v>
       </c>
       <c r="AL60">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AM60">
         <v>85</v>
@@ -15861,19 +15861,19 @@
         <v>1000</v>
       </c>
       <c r="BI60">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BJ60">
         <v>13</v>
       </c>
       <c r="BK60">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="BL60">
         <v>1000</v>
       </c>
       <c r="BM60">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BN60">
         <v>7</v>
@@ -15885,13 +15885,13 @@
         <v>18</v>
       </c>
       <c r="BQ60">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BR60">
         <v>32</v>
       </c>
       <c r="BS60">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BT60">
         <v>11</v>
@@ -15903,19 +15903,19 @@
         <v>44</v>
       </c>
       <c r="BW60">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="BX60">
         <v>50</v>
       </c>
       <c r="BY60">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BZ60">
         <v>24</v>
       </c>
       <c r="CA60">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="CB60" t="s">
         <v>350</v>
@@ -15950,7 +15950,7 @@
         <v>2.98</v>
       </c>
       <c r="J61">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K61">
         <v>4.4</v>
@@ -15974,7 +15974,7 @@
         <v>1.5</v>
       </c>
       <c r="R61">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S61">
         <v>2.2</v>
@@ -16034,31 +16034,31 @@
         <v>27</v>
       </c>
       <c r="AL61">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM61">
         <v>60</v>
       </c>
       <c r="AN61">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO61">
         <v>18</v>
       </c>
       <c r="AP61">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ61">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AR61">
         <v>21</v>
       </c>
       <c r="AS61">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AT61">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AU61">
         <v>9.199999999999999</v>
@@ -16070,7 +16070,7 @@
         <v>19</v>
       </c>
       <c r="AX61">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AY61">
         <v>9.199999999999999</v>
@@ -16082,16 +16082,16 @@
         <v>21</v>
       </c>
       <c r="BB61">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BC61">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BD61">
         <v>19.5</v>
       </c>
       <c r="BE61">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BF61">
         <v>8.199999999999999</v>
@@ -16103,7 +16103,7 @@
         <v>1000</v>
       </c>
       <c r="BI61">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BJ61">
         <v>12</v>
@@ -16115,7 +16115,7 @@
         <v>1000</v>
       </c>
       <c r="BM61">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BN61">
         <v>8.6</v>
@@ -16127,37 +16127,37 @@
         <v>22</v>
       </c>
       <c r="BQ61">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BR61">
         <v>30</v>
       </c>
       <c r="BS61">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BT61">
         <v>9.6</v>
       </c>
       <c r="BU61">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV61">
         <v>28</v>
       </c>
       <c r="BW61">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BX61">
         <v>34</v>
       </c>
       <c r="BY61">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BZ61">
         <v>20</v>
       </c>
       <c r="CA61">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="CB61" t="s">
         <v>350</v>
@@ -16180,22 +16180,22 @@
         <v>310</v>
       </c>
       <c r="F62">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="G62">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="H62">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I62">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J62">
         <v>3.55</v>
       </c>
       <c r="K62">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L62">
         <v>1.29</v>
@@ -16204,22 +16204,22 @@
         <v>1.01</v>
       </c>
       <c r="N62">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O62">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="P62">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q62">
         <v>1.74</v>
       </c>
       <c r="R62">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S62">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="T62">
         <v>1.11</v>
@@ -16228,10 +16228,10 @@
         <v>1.11</v>
       </c>
       <c r="V62">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W62">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="X62">
         <v>1000</v>
@@ -16434,7 +16434,7 @@
         <v>990</v>
       </c>
       <c r="J63">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K63">
         <v>950</v>
@@ -16470,10 +16470,10 @@
         <v>1.11</v>
       </c>
       <c r="V63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X63">
         <v>1000</v>
@@ -16703,13 +16703,13 @@
         <v>1.35</v>
       </c>
       <c r="S64">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T64">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="U64">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="V64">
         <v>1.45</v>
@@ -16906,7 +16906,7 @@
         <v>313</v>
       </c>
       <c r="F65">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G65">
         <v>3.1</v>
@@ -17313,19 +17313,19 @@
         <v>1000</v>
       </c>
       <c r="BI66">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="BJ66">
         <v>19</v>
       </c>
       <c r="BK66">
-        <v>8</v>
+        <v>1.46</v>
       </c>
       <c r="BL66">
         <v>1000</v>
       </c>
       <c r="BM66">
-        <v>21</v>
+        <v>1.58</v>
       </c>
       <c r="BN66">
         <v>10</v>
@@ -17337,13 +17337,13 @@
         <v>1000</v>
       </c>
       <c r="BQ66">
-        <v>21</v>
+        <v>1.54</v>
       </c>
       <c r="BR66">
         <v>1000</v>
       </c>
       <c r="BS66">
-        <v>21</v>
+        <v>1.58</v>
       </c>
       <c r="BT66">
         <v>6.8</v>
@@ -17355,19 +17355,19 @@
         <v>34</v>
       </c>
       <c r="BW66">
-        <v>14</v>
+        <v>1.51</v>
       </c>
       <c r="BX66">
         <v>1000</v>
       </c>
       <c r="BY66">
-        <v>21</v>
+        <v>1.55</v>
       </c>
       <c r="BZ66">
         <v>1000</v>
       </c>
       <c r="CA66">
-        <v>21</v>
+        <v>1.55</v>
       </c>
       <c r="CB66" t="s">
         <v>350</v>
@@ -17390,16 +17390,16 @@
         <v>315</v>
       </c>
       <c r="F67">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="G67">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="H67">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="I67">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J67">
         <v>2.96</v>
@@ -17414,22 +17414,22 @@
         <v>1.01</v>
       </c>
       <c r="N67">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O67">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="P67">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q67">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R67">
         <v>1.16</v>
       </c>
       <c r="S67">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T67">
         <v>1.11</v>
@@ -17438,10 +17438,10 @@
         <v>1.11</v>
       </c>
       <c r="V67">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W67">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="X67">
         <v>1000</v>
@@ -17647,22 +17647,22 @@
         <v>3.65</v>
       </c>
       <c r="K68">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L68">
         <v>1.01</v>
       </c>
       <c r="M68">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N68">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O68">
         <v>1.36</v>
       </c>
       <c r="P68">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q68">
         <v>2.08</v>
@@ -17812,7 +17812,7 @@
         <v>21</v>
       </c>
       <c r="BN68">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO68">
         <v>2.92</v>
@@ -17821,7 +17821,7 @@
         <v>17</v>
       </c>
       <c r="BQ68">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR68">
         <v>44</v>
@@ -17889,7 +17889,7 @@
         <v>3.45</v>
       </c>
       <c r="K69">
-        <v>8.199999999999999</v>
+        <v>950</v>
       </c>
       <c r="L69">
         <v>1.01</v>
@@ -18146,7 +18146,7 @@
         <v>1.14</v>
       </c>
       <c r="P70">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q70">
         <v>1.42</v>
@@ -18158,7 +18158,7 @@
         <v>2.08</v>
       </c>
       <c r="T70">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U70">
         <v>2.58</v>
@@ -18182,7 +18182,7 @@
         <v>110</v>
       </c>
       <c r="AB70">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AC70">
         <v>13.5</v>
@@ -18209,7 +18209,7 @@
         <v>24</v>
       </c>
       <c r="AK70">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL70">
         <v>28</v>
@@ -18224,16 +18224,16 @@
         <v>34</v>
       </c>
       <c r="AP70">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ70">
         <v>20</v>
       </c>
       <c r="AR70">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS70">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT70">
         <v>11.5</v>
@@ -18245,7 +18245,7 @@
         <v>15</v>
       </c>
       <c r="AW70">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX70">
         <v>11</v>
@@ -18257,7 +18257,7 @@
         <v>12.5</v>
       </c>
       <c r="BA70">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB70">
         <v>15.5</v>
@@ -18269,13 +18269,13 @@
         <v>18</v>
       </c>
       <c r="BE70">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF70">
         <v>4.9</v>
       </c>
       <c r="BG70">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH70">
         <v>1000</v>
@@ -18358,19 +18358,19 @@
         <v>319</v>
       </c>
       <c r="F71">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="G71">
         <v>990</v>
       </c>
       <c r="H71">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="I71">
-        <v>1.82</v>
+        <v>870</v>
       </c>
       <c r="J71">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="K71">
         <v>5.3</v>
@@ -18406,7 +18406,7 @@
         <v>1.9</v>
       </c>
       <c r="V71">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="W71">
         <v>1.01</v>
@@ -18600,19 +18600,19 @@
         <v>320</v>
       </c>
       <c r="F72">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G72">
         <v>990</v>
       </c>
       <c r="H72">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I72">
         <v>990</v>
       </c>
       <c r="J72">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K72">
         <v>950</v>
@@ -18648,10 +18648,10 @@
         <v>1.11</v>
       </c>
       <c r="V72">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W72">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X72">
         <v>1000</v>
@@ -18842,19 +18842,19 @@
         <v>321</v>
       </c>
       <c r="F73">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G73">
         <v>990</v>
       </c>
       <c r="H73">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I73">
         <v>990</v>
       </c>
       <c r="J73">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K73">
         <v>950</v>
@@ -18866,7 +18866,7 @@
         <v>1.01</v>
       </c>
       <c r="N73">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O73">
         <v>1.01</v>
@@ -18890,10 +18890,10 @@
         <v>1.11</v>
       </c>
       <c r="V73">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W73">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X73">
         <v>1000</v>
@@ -19084,19 +19084,19 @@
         <v>322</v>
       </c>
       <c r="F74">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G74">
         <v>990</v>
       </c>
       <c r="H74">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I74">
         <v>990</v>
       </c>
       <c r="J74">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K74">
         <v>950</v>
@@ -19108,13 +19108,13 @@
         <v>1.01</v>
       </c>
       <c r="N74">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O74">
         <v>1.01</v>
       </c>
       <c r="P74">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q74">
         <v>1.02</v>
@@ -19132,10 +19132,10 @@
         <v>1.11</v>
       </c>
       <c r="V74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X74">
         <v>1000</v>
@@ -19326,19 +19326,19 @@
         <v>323</v>
       </c>
       <c r="F75">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G75">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H75">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I75">
         <v>990</v>
       </c>
       <c r="J75">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K75">
         <v>950</v>
@@ -19350,13 +19350,13 @@
         <v>1.01</v>
       </c>
       <c r="N75">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O75">
         <v>1.01</v>
       </c>
       <c r="P75">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q75">
         <v>1.02</v>
@@ -19377,7 +19377,7 @@
         <v>1.01</v>
       </c>
       <c r="W75">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X75">
         <v>1000</v>
@@ -19580,7 +19580,7 @@
         <v>990</v>
       </c>
       <c r="J76">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="K76">
         <v>950</v>
@@ -19822,7 +19822,7 @@
         <v>990</v>
       </c>
       <c r="J77">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K77">
         <v>950</v>
@@ -19858,10 +19858,10 @@
         <v>1.11</v>
       </c>
       <c r="V77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W77">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X77">
         <v>1000</v>
@@ -20064,7 +20064,7 @@
         <v>990</v>
       </c>
       <c r="J78">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K78">
         <v>950</v>
@@ -20100,10 +20100,10 @@
         <v>1.11</v>
       </c>
       <c r="V78">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W78">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X78">
         <v>1000</v>
@@ -20306,7 +20306,7 @@
         <v>990</v>
       </c>
       <c r="J79">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K79">
         <v>950</v>
@@ -20548,7 +20548,7 @@
         <v>990</v>
       </c>
       <c r="J80">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K80">
         <v>950</v>
@@ -20563,13 +20563,13 @@
         <v>1.25</v>
       </c>
       <c r="O80">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P80">
         <v>1.25</v>
       </c>
       <c r="Q80">
-        <v>1.41</v>
+        <v>1.05</v>
       </c>
       <c r="R80">
         <v>1.12</v>
@@ -20584,10 +20584,10 @@
         <v>1.11</v>
       </c>
       <c r="V80">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W80">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X80">
         <v>1000</v>
@@ -20790,7 +20790,7 @@
         <v>990</v>
       </c>
       <c r="J81">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K81">
         <v>950</v>
@@ -20826,10 +20826,10 @@
         <v>1.11</v>
       </c>
       <c r="V81">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W81">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X81">
         <v>1000</v>
@@ -21032,7 +21032,7 @@
         <v>990</v>
       </c>
       <c r="J82">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="K82">
         <v>950</v>
@@ -21068,7 +21068,7 @@
         <v>1.11</v>
       </c>
       <c r="V82">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W82">
         <v>1.8</v>
@@ -21274,7 +21274,7 @@
         <v>990</v>
       </c>
       <c r="J83">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K83">
         <v>950</v>
@@ -21310,10 +21310,10 @@
         <v>1.11</v>
       </c>
       <c r="V83">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W83">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X83">
         <v>1000</v>
@@ -21504,19 +21504,19 @@
         <v>332</v>
       </c>
       <c r="F84">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G84">
         <v>990</v>
       </c>
       <c r="H84">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I84">
         <v>990</v>
       </c>
       <c r="J84">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K84">
         <v>950</v>
@@ -21800,7 +21800,7 @@
         <v>1.15</v>
       </c>
       <c r="X85">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y85">
         <v>10</v>
@@ -21863,7 +21863,7 @@
         <v>8.4</v>
       </c>
       <c r="AS85">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT85">
         <v>20</v>
@@ -21884,19 +21884,19 @@
         <v>4.8</v>
       </c>
       <c r="AZ85">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BA85">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB85">
         <v>5.6</v>
       </c>
       <c r="BC85">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD85">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE85">
         <v>5.5</v>
@@ -22108,10 +22108,10 @@
         <v>2.76</v>
       </c>
       <c r="AT86">
-        <v>2.28</v>
+        <v>7.6</v>
       </c>
       <c r="AU86">
-        <v>2.34</v>
+        <v>8.6</v>
       </c>
       <c r="AV86">
         <v>2.58</v>
@@ -22123,10 +22123,10 @@
         <v>7.2</v>
       </c>
       <c r="AY86">
-        <v>2.32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ86">
-        <v>2.54</v>
+        <v>17.5</v>
       </c>
       <c r="BA86">
         <v>2.76</v>
@@ -22153,13 +22153,13 @@
         <v>1000</v>
       </c>
       <c r="BI86">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="BJ86">
         <v>14.5</v>
       </c>
       <c r="BK86">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL86">
         <v>1000</v>
@@ -22171,25 +22171,25 @@
         <v>5.5</v>
       </c>
       <c r="BO86">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="BP86">
         <v>13</v>
       </c>
       <c r="BQ86">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR86">
         <v>32</v>
       </c>
       <c r="BS86">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BT86">
         <v>14.5</v>
       </c>
       <c r="BU86">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BV86">
         <v>1000</v>
@@ -22242,7 +22242,7 @@
         <v>3.6</v>
       </c>
       <c r="J87">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K87">
         <v>4.4</v>
@@ -22293,7 +22293,7 @@
         <v>34</v>
       </c>
       <c r="AA87">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB87">
         <v>18</v>
@@ -22308,7 +22308,7 @@
         <v>36</v>
       </c>
       <c r="AF87">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG87">
         <v>11.5</v>
@@ -22335,10 +22335,10 @@
         <v>8.4</v>
       </c>
       <c r="AO87">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AP87">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ87">
         <v>22</v>
@@ -22362,7 +22362,7 @@
         <v>29</v>
       </c>
       <c r="AX87">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY87">
         <v>10</v>
@@ -22395,7 +22395,7 @@
         <v>6.4</v>
       </c>
       <c r="BI87">
-        <v>3.45</v>
+        <v>2.06</v>
       </c>
       <c r="BJ87">
         <v>12</v>
@@ -22407,7 +22407,7 @@
         <v>1000</v>
       </c>
       <c r="BM87">
-        <v>21</v>
+        <v>2.94</v>
       </c>
       <c r="BN87">
         <v>8</v>
@@ -22416,16 +22416,16 @@
         <v>3.8</v>
       </c>
       <c r="BP87">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ87">
-        <v>8</v>
+        <v>2.62</v>
       </c>
       <c r="BR87">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BS87">
-        <v>11.5</v>
+        <v>2.76</v>
       </c>
       <c r="BT87">
         <v>10.5</v>
@@ -22437,19 +22437,19 @@
         <v>32</v>
       </c>
       <c r="BW87">
-        <v>13.5</v>
+        <v>2.78</v>
       </c>
       <c r="BX87">
         <v>38</v>
       </c>
       <c r="BY87">
-        <v>15</v>
+        <v>2.82</v>
       </c>
       <c r="BZ87">
         <v>17.5</v>
       </c>
       <c r="CA87">
-        <v>7.4</v>
+        <v>2.6</v>
       </c>
       <c r="CB87" t="s">
         <v>350</v>
@@ -22472,7 +22472,7 @@
         <v>336</v>
       </c>
       <c r="F88">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G88">
         <v>1.91</v>
@@ -22481,7 +22481,7 @@
         <v>3.9</v>
       </c>
       <c r="I88">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J88">
         <v>4.3</v>
@@ -22496,16 +22496,16 @@
         <v>1.02</v>
       </c>
       <c r="N88">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="O88">
         <v>1.11</v>
       </c>
       <c r="P88">
-        <v>2.9</v>
+        <v>1.25</v>
       </c>
       <c r="Q88">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="R88">
         <v>1.72</v>
@@ -22726,7 +22726,7 @@
         <v>990</v>
       </c>
       <c r="J89">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="K89">
         <v>950</v>
@@ -22753,7 +22753,7 @@
         <v>1.12</v>
       </c>
       <c r="S89">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T89">
         <v>1.11</v>
@@ -22762,7 +22762,7 @@
         <v>1.11</v>
       </c>
       <c r="V89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W89">
         <v>1.4</v>
@@ -23204,7 +23204,7 @@
         <v>3.1</v>
       </c>
       <c r="H91">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I91">
         <v>2.94</v>
@@ -23213,7 +23213,7 @@
         <v>3.4</v>
       </c>
       <c r="K91">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L91">
         <v>1.01</v>
@@ -23440,16 +23440,16 @@
         <v>340</v>
       </c>
       <c r="F92">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G92">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H92">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="I92">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="J92">
         <v>3.45</v>
@@ -23461,13 +23461,13 @@
         <v>1.01</v>
       </c>
       <c r="M92">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N92">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O92">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P92">
         <v>2</v>
@@ -23476,130 +23476,130 @@
         <v>1.89</v>
       </c>
       <c r="R92">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S92">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T92">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="U92">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="V92">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W92">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X92">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y92">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z92">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA92">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB92">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC92">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD92">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE92">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF92">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG92">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH92">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI92">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ92">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK92">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL92">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM92">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN92">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO92">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP92">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AQ92">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR92">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS92">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT92">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AU92">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV92">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW92">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX92">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AY92">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ92">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA92">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BB92">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC92">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD92">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE92">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF92">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG92">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BH92">
         <v>4.4</v>
@@ -23682,7 +23682,7 @@
         <v>341</v>
       </c>
       <c r="F93">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="G93">
         <v>1.44</v>
@@ -23706,7 +23706,7 @@
         <v>1.01</v>
       </c>
       <c r="N93">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="O93">
         <v>1.23</v>
@@ -23727,7 +23727,7 @@
         <v>1.11</v>
       </c>
       <c r="U93">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V93">
         <v>1.1</v>
@@ -24435,16 +24435,16 @@
         <v>2.96</v>
       </c>
       <c r="O96">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P96">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q96">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R96">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="S96">
         <v>2.62</v>
@@ -24656,16 +24656,16 @@
         <v>2.72</v>
       </c>
       <c r="H97">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="I97">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="J97">
         <v>2.74</v>
       </c>
       <c r="K97">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="L97">
         <v>1.01</v>
@@ -24698,7 +24698,7 @@
         <v>1.11</v>
       </c>
       <c r="V97">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W97">
         <v>1.58</v>
@@ -24892,13 +24892,13 @@
         <v>346</v>
       </c>
       <c r="F98">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="G98">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H98">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I98">
         <v>8</v>
@@ -24907,7 +24907,7 @@
         <v>3.05</v>
       </c>
       <c r="K98">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="L98">
         <v>1.01</v>
@@ -24919,7 +24919,7 @@
         <v>2.14</v>
       </c>
       <c r="O98">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="P98">
         <v>1.44</v>
@@ -24943,7 +24943,7 @@
         <v>1.14</v>
       </c>
       <c r="W98">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X98">
         <v>1000</v>
@@ -25134,7 +25134,7 @@
         <v>347</v>
       </c>
       <c r="F99">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G99">
         <v>3.2</v>
@@ -25149,7 +25149,7 @@
         <v>2.86</v>
       </c>
       <c r="K99">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L99">
         <v>1.01</v>
@@ -25299,19 +25299,19 @@
         <v>1000</v>
       </c>
       <c r="BI99">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BJ99">
         <v>17</v>
       </c>
       <c r="BK99">
-        <v>7.2</v>
+        <v>1.49</v>
       </c>
       <c r="BL99">
         <v>1000</v>
       </c>
       <c r="BM99">
-        <v>21</v>
+        <v>1.64</v>
       </c>
       <c r="BN99">
         <v>8</v>
@@ -25323,13 +25323,13 @@
         <v>44</v>
       </c>
       <c r="BQ99">
-        <v>16.5</v>
+        <v>1.58</v>
       </c>
       <c r="BR99">
         <v>1000</v>
       </c>
       <c r="BS99">
-        <v>21</v>
+        <v>1.61</v>
       </c>
       <c r="BT99">
         <v>8</v>
@@ -25341,19 +25341,19 @@
         <v>44</v>
       </c>
       <c r="BW99">
-        <v>16.5</v>
+        <v>1.58</v>
       </c>
       <c r="BX99">
         <v>1000</v>
       </c>
       <c r="BY99">
-        <v>21</v>
+        <v>1.61</v>
       </c>
       <c r="BZ99">
         <v>1000</v>
       </c>
       <c r="CA99">
-        <v>21</v>
+        <v>1.61</v>
       </c>
       <c r="CB99" t="s">
         <v>350</v>
@@ -25547,55 +25547,55 @@
         <v>1000</v>
       </c>
       <c r="BK100">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BL100">
         <v>1000</v>
       </c>
       <c r="BM100">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BN100">
         <v>1000</v>
       </c>
       <c r="BO100">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BP100">
         <v>1000</v>
       </c>
       <c r="BQ100">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BR100">
         <v>1000</v>
       </c>
       <c r="BS100">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BT100">
         <v>1000</v>
       </c>
       <c r="BU100">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BV100">
         <v>1000</v>
       </c>
       <c r="BW100">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BX100">
         <v>1000</v>
       </c>
       <c r="BY100">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BZ100">
         <v>1000</v>
       </c>
       <c r="CA100">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="CB100" t="s">
         <v>350</v>
@@ -25621,19 +25621,19 @@
         <v>2.46</v>
       </c>
       <c r="G101">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H101">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="I101">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J101">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K101">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L101">
         <v>1.01</v>
@@ -25642,46 +25642,46 @@
         <v>1.01</v>
       </c>
       <c r="N101">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O101">
         <v>1.2</v>
       </c>
       <c r="P101">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="Q101">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="R101">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S101">
-        <v>2.06</v>
+        <v>2.46</v>
       </c>
       <c r="T101">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="U101">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="V101">
         <v>1.53</v>
       </c>
       <c r="W101">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X101">
         <v>25</v>
       </c>
       <c r="Y101">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z101">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA101">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB101">
         <v>15.5</v>
@@ -25696,7 +25696,7 @@
         <v>29</v>
       </c>
       <c r="AF101">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG101">
         <v>12</v>
@@ -25708,46 +25708,46 @@
         <v>36</v>
       </c>
       <c r="AJ101">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK101">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL101">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM101">
         <v>70</v>
       </c>
       <c r="AN101">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO101">
         <v>18.5</v>
       </c>
       <c r="AP101">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AQ101">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR101">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS101">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT101">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU101">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV101">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW101">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX101">
         <v>15</v>
@@ -25771,13 +25771,13 @@
         <v>23</v>
       </c>
       <c r="BE101">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF101">
         <v>11.5</v>
       </c>
       <c r="BG101">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH101">
         <v>1000</v>
